--- a/Versão5/ABNT/Ontologia_15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0361814-B206-4C26-88D7-5D63DE9E36D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E08024-4BDD-4F7A-87A1-074D1EA03E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4079" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4079" uniqueCount="502">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1591,6 +1591,12 @@
   </si>
   <si>
     <t>Código.ABNT</t>
+  </si>
+  <si>
+    <t>1D.41.11.17</t>
+  </si>
+  <si>
+    <t>1D.41.11.14.64.00</t>
   </si>
 </sst>
 </file>
@@ -2092,7 +2098,33 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{DFB85275-A9BE-4413-B02C-324FD368C2A1}"/>
   </cellStyles>
-  <dxfs count="55">
+  <dxfs count="58">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3766,31 +3798,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:W178" headerRowCount="0" totalsRowShown="0" headerRowDxfId="54" headerRowBorderDxfId="53" tableBorderDxfId="52" totalsRowBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:W178" headerRowCount="0" totalsRowShown="0" headerRowDxfId="57" headerRowBorderDxfId="56" tableBorderDxfId="55" totalsRowBorderDxfId="54">
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="32" dataDxfId="31"/>
-    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="30" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{F0E0252A-89E6-4F99-B233-ABC4645C4906}" name="Coluna1" headerRowDxfId="28" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{88878663-DD89-49F0-9A19-ABEE711B67B6}" name="Coluna2" headerRowDxfId="26" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="24" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="22" dataDxfId="21"/>
-    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="20" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="18" dataDxfId="17"/>
-    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="16" dataDxfId="15"/>
-    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="14" dataDxfId="13"/>
-    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="12" dataDxfId="11"/>
-    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="10" dataDxfId="9"/>
-    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="8" dataDxfId="7"/>
-    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="6" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{F0E0252A-89E6-4F99-B233-ABC4645C4906}" name="Coluna1" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{88878663-DD89-49F0-9A19-ABEE711B67B6}" name="Coluna2" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="11" dataDxfId="10"/>
+    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="9" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4317,7 +4349,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46139.366928819443</v>
+        <v>46146.288617824073</v>
       </c>
       <c r="C18" s="51" t="s">
         <v>487</v>
@@ -4617,7 +4649,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="AA1:AA2">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4770,7 +4802,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4815,7 +4847,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4830,7 +4862,7 @@
   <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
     <col min="3" max="3" width="8.296875" customWidth="1"/>
     <col min="4" max="4" width="3.69921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.59765625" bestFit="1" customWidth="1"/>
@@ -12668,7 +12700,7 @@
       <c r="A111" s="7">
         <v>111</v>
       </c>
-      <c r="B111" s="13" t="s">
+      <c r="B111" s="15" t="s">
         <v>320</v>
       </c>
       <c r="C111" s="11" t="s">
@@ -12739,8 +12771,8 @@
       <c r="A112" s="7">
         <v>112</v>
       </c>
-      <c r="B112" s="14" t="s">
-        <v>320</v>
+      <c r="B112" s="15" t="s">
+        <v>500</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>499</v>
@@ -13591,8 +13623,8 @@
       <c r="A124" s="7">
         <v>124</v>
       </c>
-      <c r="B124" s="13" t="s">
-        <v>332</v>
+      <c r="B124" s="15" t="s">
+        <v>501</v>
       </c>
       <c r="C124" s="11" t="s">
         <v>499</v>
@@ -17494,14 +17526,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="R1 T1 V1 D1 F1 H1 J1 L1 N1 P1">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:W178">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">

--- a/Versão5/ABNT/Ontologia_15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAC1146-2F9A-41DF-A41F-718A481DA1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2648F0-D57E-4985-AC6F-5FD0429EF12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4386" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4386" uniqueCount="559">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1464,12 +1464,6 @@
     <t>Aviso</t>
   </si>
   <si>
-    <t>"-"</t>
-  </si>
-  <si>
-    <t>"Classificação de objetos da construção"</t>
-  </si>
-  <si>
     <t>"Norma Brasileira para a classificação de objetos da construção"</t>
   </si>
   <si>
@@ -1767,10 +1761,13 @@
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I.</t>
   </si>
   <si>
-    <t>"Classificação de objetos da construção - 1D"</t>
-  </si>
-  <si>
     <t>"[ - ]"</t>
+  </si>
+  <si>
+    <t>"Normas"</t>
+  </si>
+  <si>
+    <t>"Classificação de Projeto e Construção"</t>
   </si>
 </sst>
 </file>
@@ -2272,7 +2269,7 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0"/>
       </font>
     </dxf>
     <dxf>
@@ -2280,7 +2277,7 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -4605,7 +4602,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46148.389044212963</v>
+        <v>46148.570779861111</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>452</v>
@@ -4613,7 +4610,7 @@
     </row>
     <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>455</v>
@@ -4636,7 +4633,7 @@
     </row>
     <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="41" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B21" s="4" t="str">
         <f>_xlfn.TRANSLATE(B20,"pt","en")</f>
@@ -4816,19 +4813,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="58" t="s">
+        <v>476</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>477</v>
+      </c>
+      <c r="D2" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="E2" s="58" t="s">
         <v>479</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="F2" s="59" t="s">
         <v>480</v>
-      </c>
-      <c r="E2" s="58" t="s">
-        <v>481</v>
-      </c>
-      <c r="F2" s="59" t="s">
-        <v>482</v>
       </c>
       <c r="G2" s="53" t="s">
         <v>196</v>
@@ -4862,10 +4859,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="40" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="Q2" s="40" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="R2" s="55" t="s">
         <v>196</v>
@@ -4883,7 +4880,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="40" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="W2" s="57" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key.ABNT.",A2)</f>
@@ -4899,7 +4896,7 @@
         <v>196</v>
       </c>
       <c r="AA2" s="40" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4907,19 +4904,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="58" t="s">
+        <v>476</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>477</v>
+      </c>
+      <c r="D3" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="C3" s="59" t="s">
-        <v>479</v>
-      </c>
-      <c r="D3" s="58" t="s">
-        <v>480</v>
-      </c>
       <c r="E3" s="58" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F3" s="59" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G3" s="53" t="s">
         <v>196</v>
@@ -4953,10 +4950,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="40" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Q3" s="40" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="R3" s="55" t="s">
         <v>196</v>
@@ -4974,7 +4971,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="40" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="W3" s="57" t="str">
         <f t="shared" si="3"/>
@@ -4990,7 +4987,7 @@
         <v>196</v>
       </c>
       <c r="AA3" s="40" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4998,19 +4995,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="58" t="s">
+        <v>476</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>477</v>
+      </c>
+      <c r="D4" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="C4" s="59" t="s">
-        <v>479</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>480</v>
-      </c>
       <c r="E4" s="58" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F4" s="59" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="G4" s="53" t="s">
         <v>196</v>
@@ -5044,10 +5041,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="Q4" s="40" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="R4" s="55" t="s">
         <v>196</v>
@@ -5065,7 +5062,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="40" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="W4" s="57" t="str">
         <f t="shared" si="3"/>
@@ -5081,7 +5078,7 @@
         <v>196</v>
       </c>
       <c r="AA4" s="40" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5089,19 +5086,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="58" t="s">
+        <v>476</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>477</v>
+      </c>
+      <c r="D5" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="C5" s="59" t="s">
-        <v>479</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>480</v>
-      </c>
       <c r="E5" s="58" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G5" s="53" t="s">
         <v>196</v>
@@ -5135,10 +5132,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="40" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="Q5" s="40" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="R5" s="55" t="s">
         <v>196</v>
@@ -5156,7 +5153,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="40" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="W5" s="57" t="str">
         <f t="shared" si="3"/>
@@ -5172,7 +5169,7 @@
         <v>196</v>
       </c>
       <c r="AA5" s="40" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5180,19 +5177,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="58" t="s">
+        <v>476</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>477</v>
+      </c>
+      <c r="D6" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="C6" s="59" t="s">
-        <v>479</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>480</v>
-      </c>
       <c r="E6" s="58" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G6" s="53" t="s">
         <v>196</v>
@@ -5226,10 +5223,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="40" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Q6" s="40" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="R6" s="55" t="s">
         <v>196</v>
@@ -5247,7 +5244,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="40" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="W6" s="57" t="str">
         <f t="shared" si="3"/>
@@ -5263,7 +5260,7 @@
         <v>196</v>
       </c>
       <c r="AA6" s="40" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5283,7 +5280,7 @@
         <v>430</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>196</v>
@@ -5317,10 +5314,10 @@
         <v>ABNT.0M</v>
       </c>
       <c r="P7" s="54" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Q7" s="54" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="R7" s="55" t="s">
         <v>196</v>
@@ -5351,10 +5348,10 @@
         <v>196</v>
       </c>
       <c r="Z7" s="40" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AA7" s="60" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5374,7 +5371,7 @@
         <v>430</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>196</v>
@@ -5408,10 +5405,10 @@
         <v>ABNT.0P</v>
       </c>
       <c r="P8" s="54" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="Q8" s="54" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="R8" s="55" t="s">
         <v>196</v>
@@ -5442,10 +5439,10 @@
         <v>196</v>
       </c>
       <c r="Z8" s="40" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AA8" s="60" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5465,7 +5462,7 @@
         <v>430</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>196</v>
@@ -5499,10 +5496,10 @@
         <v>ABNT.1D</v>
       </c>
       <c r="P9" s="54" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q9" s="54" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="R9" s="55" t="s">
         <v>196</v>
@@ -5536,7 +5533,7 @@
         <v>377</v>
       </c>
       <c r="AA9" s="60" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5556,7 +5553,7 @@
         <v>430</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>196</v>
@@ -5590,10 +5587,10 @@
         <v>ABNT.1F</v>
       </c>
       <c r="P10" s="54" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="Q10" s="54" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R10" s="55" t="s">
         <v>196</v>
@@ -5624,10 +5621,10 @@
         <v>196</v>
       </c>
       <c r="Z10" s="40" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AA10" s="60" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5647,7 +5644,7 @@
         <v>430</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>196</v>
@@ -5681,10 +5678,10 @@
         <v>ABNT.1S</v>
       </c>
       <c r="P11" s="54" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="Q11" s="54" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="R11" s="55" t="s">
         <v>196</v>
@@ -5715,10 +5712,10 @@
         <v>196</v>
       </c>
       <c r="Z11" s="40" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AA11" s="60" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5738,7 +5735,7 @@
         <v>430</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>196</v>
@@ -5772,10 +5769,10 @@
         <v>ABNT.2C</v>
       </c>
       <c r="P12" s="54" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Q12" s="54" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="R12" s="55" t="s">
         <v>196</v>
@@ -5806,10 +5803,10 @@
         <v>196</v>
       </c>
       <c r="Z12" s="40" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AA12" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5829,7 +5826,7 @@
         <v>430</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>196</v>
@@ -5863,10 +5860,10 @@
         <v>ABNT.2N</v>
       </c>
       <c r="P13" s="54" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Q13" s="54" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="R13" s="55" t="s">
         <v>196</v>
@@ -5897,10 +5894,10 @@
         <v>196</v>
       </c>
       <c r="Z13" s="40" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="AA13" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5920,7 +5917,7 @@
         <v>430</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>196</v>
@@ -5954,10 +5951,10 @@
         <v>ABNT.2Q</v>
       </c>
       <c r="P14" s="54" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Q14" s="54" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="R14" s="55" t="s">
         <v>196</v>
@@ -5988,10 +5985,10 @@
         <v>196</v>
       </c>
       <c r="Z14" s="40" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AA14" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6011,7 +6008,7 @@
         <v>430</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>196</v>
@@ -6045,10 +6042,10 @@
         <v>ABNT.3E</v>
       </c>
       <c r="P15" s="54" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="Q15" s="54" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="R15" s="55" t="s">
         <v>196</v>
@@ -6079,10 +6076,10 @@
         <v>196</v>
       </c>
       <c r="Z15" s="40" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AA15" s="60" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6102,7 +6099,7 @@
         <v>430</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>196</v>
@@ -6136,10 +6133,10 @@
         <v>ABNT.3R</v>
       </c>
       <c r="P16" s="54" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Q16" s="54" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="R16" s="55" t="s">
         <v>196</v>
@@ -6170,10 +6167,10 @@
         <v>196</v>
       </c>
       <c r="Z16" s="40" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AA16" s="60" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6193,7 +6190,7 @@
         <v>430</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>196</v>
@@ -6227,10 +6224,10 @@
         <v>ABNT.4A</v>
       </c>
       <c r="P17" s="54" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="Q17" s="54" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="R17" s="55" t="s">
         <v>196</v>
@@ -6261,10 +6258,10 @@
         <v>196</v>
       </c>
       <c r="Z17" s="40" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AA17" s="60" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6284,7 +6281,7 @@
         <v>430</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>196</v>
@@ -6318,10 +6315,10 @@
         <v>ABNT.4U</v>
       </c>
       <c r="P18" s="54" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Q18" s="54" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="R18" s="55" t="s">
         <v>196</v>
@@ -6352,10 +6349,10 @@
         <v>196</v>
       </c>
       <c r="Z18" s="40" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AA18" s="60" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6375,7 +6372,7 @@
         <v>430</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G19" s="35" t="s">
         <v>196</v>
@@ -6409,10 +6406,10 @@
         <v>ABNT.5I</v>
       </c>
       <c r="P19" s="54" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="Q19" s="54" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="R19" s="55" t="s">
         <v>196</v>
@@ -6443,10 +6440,10 @@
         <v>196</v>
       </c>
       <c r="Z19" s="40" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AA19" s="60" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -6682,9 +6679,9 @@
     <col min="6" max="6" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.1640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="41.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.33203125" bestFit="1" customWidth="1"/>
@@ -6787,16 +6784,16 @@
         <v>383</v>
       </c>
       <c r="F2" s="47" t="s">
-        <v>375</v>
+        <v>196</v>
       </c>
       <c r="G2" s="48" t="s">
-        <v>457</v>
+        <v>196</v>
       </c>
       <c r="H2" s="47" t="s">
         <v>376</v>
       </c>
       <c r="I2" s="48" t="s">
-        <v>458</v>
+        <v>557</v>
       </c>
       <c r="J2" s="47" t="s">
         <v>436</v>
@@ -6808,7 +6805,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="49" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="N2" s="47" t="s">
         <v>196</v>
@@ -6863,13 +6860,13 @@
       <c r="G3" s="37" t="s">
         <v>379</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="47" t="s">
         <v>376</v>
       </c>
       <c r="I3" s="48" t="s">
-        <v>458</v>
-      </c>
-      <c r="J3" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="J3" s="47" t="s">
         <v>436</v>
       </c>
       <c r="K3" s="48" t="s">
@@ -6920,7 +6917,7 @@
         <v>377</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D4" s="36" t="s">
         <v>381</v>
@@ -6934,13 +6931,13 @@
       <c r="G4" s="37" t="s">
         <v>379</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="47" t="s">
         <v>376</v>
       </c>
       <c r="I4" s="48" t="s">
-        <v>458</v>
-      </c>
-      <c r="J4" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="J4" s="47" t="s">
         <v>436</v>
       </c>
       <c r="K4" s="48" t="s">
@@ -6991,7 +6988,7 @@
         <v>203</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D5" s="36" t="s">
         <v>381</v>
@@ -7024,16 +7021,16 @@
         <v>18</v>
       </c>
       <c r="N5" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O5" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P5" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q5" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R5" s="50" t="s">
         <v>196</v>
@@ -7062,7 +7059,7 @@
         <v>204</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D6" s="36" t="s">
         <v>381</v>
@@ -7095,16 +7092,16 @@
         <v>19</v>
       </c>
       <c r="N6" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O6" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P6" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q6" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R6" s="50" t="s">
         <v>196</v>
@@ -7133,7 +7130,7 @@
         <v>205</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>381</v>
@@ -7166,16 +7163,16 @@
         <v>20</v>
       </c>
       <c r="N7" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O7" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P7" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q7" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R7" s="50" t="s">
         <v>196</v>
@@ -7204,7 +7201,7 @@
         <v>206</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D8" s="36" t="s">
         <v>381</v>
@@ -7237,16 +7234,16 @@
         <v>21</v>
       </c>
       <c r="N8" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O8" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P8" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q8" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R8" s="50" t="s">
         <v>196</v>
@@ -7275,7 +7272,7 @@
         <v>207</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D9" s="36" t="s">
         <v>381</v>
@@ -7308,16 +7305,16 @@
         <v>22</v>
       </c>
       <c r="N9" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O9" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P9" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q9" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R9" s="50" t="s">
         <v>196</v>
@@ -7346,7 +7343,7 @@
         <v>208</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D10" s="36" t="s">
         <v>381</v>
@@ -7379,16 +7376,16 @@
         <v>23</v>
       </c>
       <c r="N10" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O10" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P10" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q10" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R10" s="50" t="s">
         <v>196</v>
@@ -7417,7 +7414,7 @@
         <v>209</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D11" s="36" t="s">
         <v>381</v>
@@ -7450,16 +7447,16 @@
         <v>24</v>
       </c>
       <c r="N11" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O11" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P11" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q11" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R11" s="50" t="s">
         <v>196</v>
@@ -7488,7 +7485,7 @@
         <v>210</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D12" s="36" t="s">
         <v>381</v>
@@ -7521,16 +7518,16 @@
         <v>25</v>
       </c>
       <c r="N12" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O12" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P12" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q12" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R12" s="50" t="s">
         <v>196</v>
@@ -7559,7 +7556,7 @@
         <v>211</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D13" s="36" t="s">
         <v>381</v>
@@ -7592,16 +7589,16 @@
         <v>26</v>
       </c>
       <c r="N13" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O13" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P13" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q13" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R13" s="50" t="s">
         <v>196</v>
@@ -7630,7 +7627,7 @@
         <v>212</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D14" s="36" t="s">
         <v>381</v>
@@ -7663,16 +7660,16 @@
         <v>27</v>
       </c>
       <c r="N14" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O14" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P14" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q14" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R14" s="50" t="s">
         <v>196</v>
@@ -7701,7 +7698,7 @@
         <v>213</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D15" s="36" t="s">
         <v>381</v>
@@ -7734,16 +7731,16 @@
         <v>28</v>
       </c>
       <c r="N15" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O15" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P15" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q15" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R15" s="50" t="s">
         <v>196</v>
@@ -7772,7 +7769,7 @@
         <v>214</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D16" s="36" t="s">
         <v>381</v>
@@ -7805,16 +7802,16 @@
         <v>29</v>
       </c>
       <c r="N16" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O16" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P16" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q16" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R16" s="50" t="s">
         <v>196</v>
@@ -7843,7 +7840,7 @@
         <v>215</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D17" s="36" t="s">
         <v>381</v>
@@ -7876,16 +7873,16 @@
         <v>30</v>
       </c>
       <c r="N17" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O17" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P17" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q17" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R17" s="50" t="s">
         <v>196</v>
@@ -7914,7 +7911,7 @@
         <v>216</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D18" s="36" t="s">
         <v>381</v>
@@ -7947,16 +7944,16 @@
         <v>31</v>
       </c>
       <c r="N18" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O18" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P18" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q18" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R18" s="50" t="s">
         <v>196</v>
@@ -7985,7 +7982,7 @@
         <v>217</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D19" s="36" t="s">
         <v>381</v>
@@ -8018,16 +8015,16 @@
         <v>32</v>
       </c>
       <c r="N19" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O19" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P19" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q19" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R19" s="50" t="s">
         <v>196</v>
@@ -8056,7 +8053,7 @@
         <v>218</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D20" s="36" t="s">
         <v>381</v>
@@ -8089,16 +8086,16 @@
         <v>33</v>
       </c>
       <c r="N20" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O20" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P20" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q20" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R20" s="50" t="s">
         <v>196</v>
@@ -8127,7 +8124,7 @@
         <v>219</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D21" s="36" t="s">
         <v>381</v>
@@ -8160,16 +8157,16 @@
         <v>34</v>
       </c>
       <c r="N21" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O21" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P21" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q21" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R21" s="50" t="s">
         <v>196</v>
@@ -8198,7 +8195,7 @@
         <v>220</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D22" s="36" t="s">
         <v>381</v>
@@ -8231,16 +8228,16 @@
         <v>35</v>
       </c>
       <c r="N22" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O22" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P22" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q22" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R22" s="50" t="s">
         <v>196</v>
@@ -8269,7 +8266,7 @@
         <v>221</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D23" s="36" t="s">
         <v>381</v>
@@ -8302,16 +8299,16 @@
         <v>36</v>
       </c>
       <c r="N23" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O23" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P23" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q23" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R23" s="50" t="s">
         <v>196</v>
@@ -8340,7 +8337,7 @@
         <v>222</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D24" s="36" t="s">
         <v>381</v>
@@ -8373,16 +8370,16 @@
         <v>37</v>
       </c>
       <c r="N24" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O24" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P24" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q24" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R24" s="50" t="s">
         <v>196</v>
@@ -8411,7 +8408,7 @@
         <v>223</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D25" s="36" t="s">
         <v>381</v>
@@ -8444,16 +8441,16 @@
         <v>38</v>
       </c>
       <c r="N25" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O25" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P25" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q25" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R25" s="50" t="s">
         <v>196</v>
@@ -8482,7 +8479,7 @@
         <v>224</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D26" s="36" t="s">
         <v>381</v>
@@ -8515,16 +8512,16 @@
         <v>39</v>
       </c>
       <c r="N26" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O26" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P26" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q26" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R26" s="50" t="s">
         <v>196</v>
@@ -8553,7 +8550,7 @@
         <v>225</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D27" s="36" t="s">
         <v>381</v>
@@ -8586,16 +8583,16 @@
         <v>40</v>
       </c>
       <c r="N27" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O27" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P27" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q27" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R27" s="50" t="s">
         <v>196</v>
@@ -8624,7 +8621,7 @@
         <v>226</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D28" s="36" t="s">
         <v>381</v>
@@ -8657,16 +8654,16 @@
         <v>41</v>
       </c>
       <c r="N28" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O28" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P28" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q28" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R28" s="50" t="s">
         <v>196</v>
@@ -8695,7 +8692,7 @@
         <v>227</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D29" s="36" t="s">
         <v>381</v>
@@ -8728,16 +8725,16 @@
         <v>437</v>
       </c>
       <c r="N29" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O29" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P29" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q29" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R29" s="50" t="s">
         <v>196</v>
@@ -8766,7 +8763,7 @@
         <v>228</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D30" s="36" t="s">
         <v>381</v>
@@ -8799,16 +8796,16 @@
         <v>42</v>
       </c>
       <c r="N30" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O30" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P30" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q30" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R30" s="50" t="s">
         <v>196</v>
@@ -8837,7 +8834,7 @@
         <v>229</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D31" s="36" t="s">
         <v>381</v>
@@ -8870,16 +8867,16 @@
         <v>43</v>
       </c>
       <c r="N31" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O31" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P31" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q31" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R31" s="50" t="s">
         <v>196</v>
@@ -8908,7 +8905,7 @@
         <v>230</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D32" s="36" t="s">
         <v>381</v>
@@ -8941,16 +8938,16 @@
         <v>44</v>
       </c>
       <c r="N32" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O32" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P32" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q32" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R32" s="50" t="s">
         <v>196</v>
@@ -8979,7 +8976,7 @@
         <v>231</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D33" s="36" t="s">
         <v>381</v>
@@ -9012,16 +9009,16 @@
         <v>45</v>
       </c>
       <c r="N33" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O33" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P33" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q33" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R33" s="50" t="s">
         <v>196</v>
@@ -9050,7 +9047,7 @@
         <v>232</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D34" s="36" t="s">
         <v>381</v>
@@ -9083,16 +9080,16 @@
         <v>46</v>
       </c>
       <c r="N34" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O34" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P34" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q34" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R34" s="50" t="s">
         <v>196</v>
@@ -9121,7 +9118,7 @@
         <v>233</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D35" s="36" t="s">
         <v>381</v>
@@ -9154,16 +9151,16 @@
         <v>47</v>
       </c>
       <c r="N35" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O35" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P35" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q35" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R35" s="50" t="s">
         <v>196</v>
@@ -9192,7 +9189,7 @@
         <v>234</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D36" s="36" t="s">
         <v>381</v>
@@ -9225,16 +9222,16 @@
         <v>48</v>
       </c>
       <c r="N36" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O36" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P36" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q36" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R36" s="50" t="s">
         <v>196</v>
@@ -9263,7 +9260,7 @@
         <v>235</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D37" s="36" t="s">
         <v>381</v>
@@ -9296,16 +9293,16 @@
         <v>49</v>
       </c>
       <c r="N37" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O37" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P37" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q37" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R37" s="50" t="s">
         <v>196</v>
@@ -9334,7 +9331,7 @@
         <v>236</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D38" s="36" t="s">
         <v>381</v>
@@ -9367,16 +9364,16 @@
         <v>50</v>
       </c>
       <c r="N38" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O38" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P38" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q38" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R38" s="50" t="s">
         <v>196</v>
@@ -9405,7 +9402,7 @@
         <v>237</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D39" s="36" t="s">
         <v>381</v>
@@ -9438,16 +9435,16 @@
         <v>51</v>
       </c>
       <c r="N39" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O39" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P39" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q39" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R39" s="50" t="s">
         <v>196</v>
@@ -9476,7 +9473,7 @@
         <v>238</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D40" s="36" t="s">
         <v>381</v>
@@ -9509,16 +9506,16 @@
         <v>52</v>
       </c>
       <c r="N40" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O40" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P40" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q40" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R40" s="50" t="s">
         <v>196</v>
@@ -9547,7 +9544,7 @@
         <v>239</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D41" s="36" t="s">
         <v>381</v>
@@ -9580,16 +9577,16 @@
         <v>53</v>
       </c>
       <c r="N41" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O41" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P41" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q41" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R41" s="50" t="s">
         <v>196</v>
@@ -9618,7 +9615,7 @@
         <v>240</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D42" s="36" t="s">
         <v>381</v>
@@ -9651,16 +9648,16 @@
         <v>54</v>
       </c>
       <c r="N42" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O42" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P42" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q42" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R42" s="50" t="s">
         <v>196</v>
@@ -9689,7 +9686,7 @@
         <v>241</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D43" s="36" t="s">
         <v>381</v>
@@ -9722,16 +9719,16 @@
         <v>15</v>
       </c>
       <c r="N43" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O43" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P43" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q43" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R43" s="50" t="s">
         <v>196</v>
@@ -9760,7 +9757,7 @@
         <v>242</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D44" s="36" t="s">
         <v>381</v>
@@ -9793,16 +9790,16 @@
         <v>55</v>
       </c>
       <c r="N44" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O44" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P44" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q44" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R44" s="50" t="s">
         <v>196</v>
@@ -9831,7 +9828,7 @@
         <v>243</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D45" s="36" t="s">
         <v>381</v>
@@ -9864,16 +9861,16 @@
         <v>56</v>
       </c>
       <c r="N45" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O45" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P45" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q45" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R45" s="50" t="s">
         <v>196</v>
@@ -9902,7 +9899,7 @@
         <v>244</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D46" s="36" t="s">
         <v>381</v>
@@ -9935,16 +9932,16 @@
         <v>57</v>
       </c>
       <c r="N46" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O46" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P46" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q46" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R46" s="50" t="s">
         <v>196</v>
@@ -9973,7 +9970,7 @@
         <v>245</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D47" s="36" t="s">
         <v>381</v>
@@ -10006,16 +10003,16 @@
         <v>58</v>
       </c>
       <c r="N47" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O47" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P47" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q47" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R47" s="50" t="s">
         <v>196</v>
@@ -10044,7 +10041,7 @@
         <v>246</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D48" s="36" t="s">
         <v>381</v>
@@ -10077,16 +10074,16 @@
         <v>59</v>
       </c>
       <c r="N48" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O48" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P48" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q48" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R48" s="50" t="s">
         <v>196</v>
@@ -10115,7 +10112,7 @@
         <v>247</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D49" s="36" t="s">
         <v>381</v>
@@ -10148,16 +10145,16 @@
         <v>60</v>
       </c>
       <c r="N49" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O49" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P49" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q49" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R49" s="50" t="s">
         <v>196</v>
@@ -10186,7 +10183,7 @@
         <v>248</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D50" s="36" t="s">
         <v>381</v>
@@ -10219,16 +10216,16 @@
         <v>61</v>
       </c>
       <c r="N50" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O50" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P50" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q50" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R50" s="50" t="s">
         <v>196</v>
@@ -10257,7 +10254,7 @@
         <v>249</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D51" s="36" t="s">
         <v>381</v>
@@ -10290,16 +10287,16 @@
         <v>62</v>
       </c>
       <c r="N51" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O51" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P51" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q51" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R51" s="50" t="s">
         <v>196</v>
@@ -10328,7 +10325,7 @@
         <v>250</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D52" s="36" t="s">
         <v>381</v>
@@ -10361,16 +10358,16 @@
         <v>63</v>
       </c>
       <c r="N52" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O52" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P52" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q52" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R52" s="50" t="s">
         <v>196</v>
@@ -10399,7 +10396,7 @@
         <v>251</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D53" s="36" t="s">
         <v>381</v>
@@ -10432,16 +10429,16 @@
         <v>64</v>
       </c>
       <c r="N53" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O53" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P53" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q53" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R53" s="50" t="s">
         <v>196</v>
@@ -10470,7 +10467,7 @@
         <v>252</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D54" s="36" t="s">
         <v>381</v>
@@ -10503,16 +10500,16 @@
         <v>65</v>
       </c>
       <c r="N54" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O54" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P54" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q54" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R54" s="50" t="s">
         <v>196</v>
@@ -10541,7 +10538,7 @@
         <v>253</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D55" s="36" t="s">
         <v>381</v>
@@ -10574,16 +10571,16 @@
         <v>66</v>
       </c>
       <c r="N55" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O55" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P55" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q55" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R55" s="50" t="s">
         <v>196</v>
@@ -10612,7 +10609,7 @@
         <v>254</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D56" s="36" t="s">
         <v>381</v>
@@ -10645,16 +10642,16 @@
         <v>67</v>
       </c>
       <c r="N56" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O56" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P56" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q56" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R56" s="50" t="s">
         <v>196</v>
@@ -10683,7 +10680,7 @@
         <v>255</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D57" s="36" t="s">
         <v>381</v>
@@ -10716,16 +10713,16 @@
         <v>68</v>
       </c>
       <c r="N57" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O57" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P57" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q57" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R57" s="50" t="s">
         <v>196</v>
@@ -10754,7 +10751,7 @@
         <v>256</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D58" s="36" t="s">
         <v>381</v>
@@ -10787,16 +10784,16 @@
         <v>69</v>
       </c>
       <c r="N58" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O58" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P58" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q58" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R58" s="50" t="s">
         <v>196</v>
@@ -10825,7 +10822,7 @@
         <v>257</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D59" s="36" t="s">
         <v>381</v>
@@ -10858,16 +10855,16 @@
         <v>70</v>
       </c>
       <c r="N59" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O59" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P59" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q59" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R59" s="50" t="s">
         <v>196</v>
@@ -10896,7 +10893,7 @@
         <v>258</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D60" s="36" t="s">
         <v>381</v>
@@ -10929,16 +10926,16 @@
         <v>71</v>
       </c>
       <c r="N60" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O60" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P60" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q60" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R60" s="50" t="s">
         <v>196</v>
@@ -10967,7 +10964,7 @@
         <v>259</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D61" s="36" t="s">
         <v>381</v>
@@ -11000,16 +10997,16 @@
         <v>72</v>
       </c>
       <c r="N61" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O61" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P61" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q61" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R61" s="50" t="s">
         <v>196</v>
@@ -11038,7 +11035,7 @@
         <v>260</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D62" s="36" t="s">
         <v>381</v>
@@ -11071,16 +11068,16 @@
         <v>73</v>
       </c>
       <c r="N62" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O62" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P62" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q62" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R62" s="50" t="s">
         <v>196</v>
@@ -11109,7 +11106,7 @@
         <v>261</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D63" s="36" t="s">
         <v>381</v>
@@ -11142,16 +11139,16 @@
         <v>74</v>
       </c>
       <c r="N63" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O63" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P63" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q63" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R63" s="50" t="s">
         <v>196</v>
@@ -11180,7 +11177,7 @@
         <v>262</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D64" s="36" t="s">
         <v>381</v>
@@ -11213,16 +11210,16 @@
         <v>75</v>
       </c>
       <c r="N64" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O64" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P64" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q64" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R64" s="50" t="s">
         <v>196</v>
@@ -11251,7 +11248,7 @@
         <v>263</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D65" s="36" t="s">
         <v>381</v>
@@ -11281,19 +11278,19 @@
         <v>1</v>
       </c>
       <c r="M65" s="11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="N65" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O65" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P65" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q65" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R65" s="50" t="s">
         <v>196</v>
@@ -11322,7 +11319,7 @@
         <v>264</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D66" s="36" t="s">
         <v>381</v>
@@ -11352,19 +11349,19 @@
         <v>1</v>
       </c>
       <c r="M66" s="11" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="N66" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O66" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P66" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q66" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R66" s="50" t="s">
         <v>196</v>
@@ -11393,7 +11390,7 @@
         <v>265</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D67" s="36" t="s">
         <v>381</v>
@@ -11426,16 +11423,16 @@
         <v>76</v>
       </c>
       <c r="N67" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O67" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P67" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q67" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R67" s="50" t="s">
         <v>196</v>
@@ -11464,7 +11461,7 @@
         <v>266</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D68" s="36" t="s">
         <v>381</v>
@@ -11488,7 +11485,7 @@
         <v>436</v>
       </c>
       <c r="K68" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L68" s="36" t="s">
         <v>1</v>
@@ -11497,16 +11494,16 @@
         <v>77</v>
       </c>
       <c r="N68" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O68" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P68" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q68" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R68" s="50" t="s">
         <v>196</v>
@@ -11535,7 +11532,7 @@
         <v>267</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D69" s="36" t="s">
         <v>381</v>
@@ -11559,7 +11556,7 @@
         <v>436</v>
       </c>
       <c r="K69" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L69" s="36" t="s">
         <v>1</v>
@@ -11568,16 +11565,16 @@
         <v>78</v>
       </c>
       <c r="N69" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O69" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P69" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q69" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R69" s="50" t="s">
         <v>196</v>
@@ -11606,7 +11603,7 @@
         <v>268</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D70" s="36" t="s">
         <v>381</v>
@@ -11630,7 +11627,7 @@
         <v>436</v>
       </c>
       <c r="K70" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L70" s="36" t="s">
         <v>1</v>
@@ -11639,16 +11636,16 @@
         <v>79</v>
       </c>
       <c r="N70" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O70" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P70" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q70" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R70" s="50" t="s">
         <v>196</v>
@@ -11677,7 +11674,7 @@
         <v>269</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D71" s="36" t="s">
         <v>381</v>
@@ -11701,7 +11698,7 @@
         <v>436</v>
       </c>
       <c r="K71" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L71" s="36" t="s">
         <v>1</v>
@@ -11710,16 +11707,16 @@
         <v>80</v>
       </c>
       <c r="N71" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O71" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P71" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q71" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R71" s="50" t="s">
         <v>196</v>
@@ -11748,7 +11745,7 @@
         <v>270</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D72" s="36" t="s">
         <v>381</v>
@@ -11772,25 +11769,25 @@
         <v>436</v>
       </c>
       <c r="K72" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L72" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M72" s="11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="N72" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O72" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P72" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q72" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R72" s="50" t="s">
         <v>196</v>
@@ -11819,7 +11816,7 @@
         <v>271</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D73" s="36" t="s">
         <v>381</v>
@@ -11843,7 +11840,7 @@
         <v>436</v>
       </c>
       <c r="K73" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L73" s="36" t="s">
         <v>1</v>
@@ -11852,16 +11849,16 @@
         <v>81</v>
       </c>
       <c r="N73" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O73" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P73" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q73" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R73" s="50" t="s">
         <v>196</v>
@@ -11890,7 +11887,7 @@
         <v>272</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D74" s="36" t="s">
         <v>381</v>
@@ -11914,7 +11911,7 @@
         <v>436</v>
       </c>
       <c r="K74" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L74" s="36" t="s">
         <v>1</v>
@@ -11923,16 +11920,16 @@
         <v>82</v>
       </c>
       <c r="N74" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O74" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P74" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q74" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R74" s="50" t="s">
         <v>196</v>
@@ -11961,7 +11958,7 @@
         <v>273</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D75" s="36" t="s">
         <v>381</v>
@@ -11985,7 +11982,7 @@
         <v>436</v>
       </c>
       <c r="K75" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L75" s="36" t="s">
         <v>1</v>
@@ -11994,16 +11991,16 @@
         <v>83</v>
       </c>
       <c r="N75" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O75" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P75" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q75" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R75" s="50" t="s">
         <v>196</v>
@@ -12032,7 +12029,7 @@
         <v>274</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D76" s="36" t="s">
         <v>381</v>
@@ -12056,7 +12053,7 @@
         <v>436</v>
       </c>
       <c r="K76" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L76" s="36" t="s">
         <v>1</v>
@@ -12065,16 +12062,16 @@
         <v>84</v>
       </c>
       <c r="N76" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O76" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P76" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q76" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R76" s="50" t="s">
         <v>196</v>
@@ -12103,7 +12100,7 @@
         <v>275</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D77" s="36" t="s">
         <v>381</v>
@@ -12127,7 +12124,7 @@
         <v>436</v>
       </c>
       <c r="K77" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L77" s="36" t="s">
         <v>1</v>
@@ -12136,16 +12133,16 @@
         <v>85</v>
       </c>
       <c r="N77" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O77" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P77" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q77" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R77" s="50" t="s">
         <v>196</v>
@@ -12174,7 +12171,7 @@
         <v>276</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D78" s="36" t="s">
         <v>381</v>
@@ -12198,7 +12195,7 @@
         <v>436</v>
       </c>
       <c r="K78" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L78" s="36" t="s">
         <v>1</v>
@@ -12207,16 +12204,16 @@
         <v>86</v>
       </c>
       <c r="N78" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O78" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P78" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q78" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R78" s="50" t="s">
         <v>196</v>
@@ -12245,7 +12242,7 @@
         <v>277</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D79" s="36" t="s">
         <v>381</v>
@@ -12269,7 +12266,7 @@
         <v>436</v>
       </c>
       <c r="K79" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L79" s="36" t="s">
         <v>1</v>
@@ -12278,16 +12275,16 @@
         <v>87</v>
       </c>
       <c r="N79" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O79" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P79" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q79" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R79" s="50" t="s">
         <v>196</v>
@@ -12316,7 +12313,7 @@
         <v>278</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D80" s="36" t="s">
         <v>381</v>
@@ -12340,7 +12337,7 @@
         <v>436</v>
       </c>
       <c r="K80" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L80" s="36" t="s">
         <v>1</v>
@@ -12349,16 +12346,16 @@
         <v>88</v>
       </c>
       <c r="N80" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O80" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P80" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q80" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R80" s="50" t="s">
         <v>196</v>
@@ -12387,7 +12384,7 @@
         <v>279</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D81" s="36" t="s">
         <v>381</v>
@@ -12411,7 +12408,7 @@
         <v>436</v>
       </c>
       <c r="K81" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L81" s="36" t="s">
         <v>1</v>
@@ -12420,16 +12417,16 @@
         <v>89</v>
       </c>
       <c r="N81" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O81" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P81" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q81" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R81" s="50" t="s">
         <v>196</v>
@@ -12458,7 +12455,7 @@
         <v>280</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D82" s="36" t="s">
         <v>381</v>
@@ -12482,7 +12479,7 @@
         <v>436</v>
       </c>
       <c r="K82" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L82" s="36" t="s">
         <v>1</v>
@@ -12491,16 +12488,16 @@
         <v>90</v>
       </c>
       <c r="N82" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O82" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P82" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q82" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R82" s="50" t="s">
         <v>196</v>
@@ -12529,7 +12526,7 @@
         <v>281</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D83" s="36" t="s">
         <v>381</v>
@@ -12553,25 +12550,25 @@
         <v>436</v>
       </c>
       <c r="K83" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L83" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M83" s="11" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N83" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O83" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P83" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q83" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R83" s="50" t="s">
         <v>196</v>
@@ -12600,7 +12597,7 @@
         <v>282</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D84" s="36" t="s">
         <v>381</v>
@@ -12624,7 +12621,7 @@
         <v>436</v>
       </c>
       <c r="K84" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L84" s="36" t="s">
         <v>1</v>
@@ -12633,16 +12630,16 @@
         <v>91</v>
       </c>
       <c r="N84" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O84" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P84" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q84" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R84" s="50" t="s">
         <v>196</v>
@@ -12671,7 +12668,7 @@
         <v>283</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D85" s="36" t="s">
         <v>381</v>
@@ -12695,7 +12692,7 @@
         <v>436</v>
       </c>
       <c r="K85" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L85" s="36" t="s">
         <v>1</v>
@@ -12704,16 +12701,16 @@
         <v>92</v>
       </c>
       <c r="N85" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O85" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P85" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q85" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R85" s="50" t="s">
         <v>196</v>
@@ -12742,7 +12739,7 @@
         <v>284</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D86" s="36" t="s">
         <v>381</v>
@@ -12766,7 +12763,7 @@
         <v>436</v>
       </c>
       <c r="K86" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L86" s="36" t="s">
         <v>1</v>
@@ -12775,16 +12772,16 @@
         <v>93</v>
       </c>
       <c r="N86" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O86" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P86" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q86" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R86" s="50" t="s">
         <v>196</v>
@@ -12813,7 +12810,7 @@
         <v>285</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D87" s="36" t="s">
         <v>381</v>
@@ -12837,7 +12834,7 @@
         <v>436</v>
       </c>
       <c r="K87" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L87" s="36" t="s">
         <v>1</v>
@@ -12846,16 +12843,16 @@
         <v>94</v>
       </c>
       <c r="N87" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O87" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P87" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q87" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R87" s="50" t="s">
         <v>196</v>
@@ -12884,7 +12881,7 @@
         <v>286</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D88" s="36" t="s">
         <v>381</v>
@@ -12917,16 +12914,16 @@
         <v>95</v>
       </c>
       <c r="N88" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O88" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P88" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q88" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R88" s="50" t="s">
         <v>196</v>
@@ -12955,7 +12952,7 @@
         <v>287</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D89" s="36" t="s">
         <v>381</v>
@@ -12988,16 +12985,16 @@
         <v>96</v>
       </c>
       <c r="N89" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O89" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P89" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q89" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R89" s="50" t="s">
         <v>196</v>
@@ -13026,7 +13023,7 @@
         <v>288</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D90" s="36" t="s">
         <v>381</v>
@@ -13059,16 +13056,16 @@
         <v>97</v>
       </c>
       <c r="N90" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O90" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P90" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q90" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R90" s="50" t="s">
         <v>196</v>
@@ -13097,7 +13094,7 @@
         <v>289</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D91" s="36" t="s">
         <v>381</v>
@@ -13130,16 +13127,16 @@
         <v>98</v>
       </c>
       <c r="N91" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O91" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P91" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q91" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R91" s="50" t="s">
         <v>196</v>
@@ -13168,7 +13165,7 @@
         <v>290</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D92" s="36" t="s">
         <v>381</v>
@@ -13198,19 +13195,19 @@
         <v>1</v>
       </c>
       <c r="M92" s="11" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N92" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O92" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P92" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q92" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R92" s="50" t="s">
         <v>196</v>
@@ -13239,7 +13236,7 @@
         <v>291</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D93" s="36" t="s">
         <v>381</v>
@@ -13272,16 +13269,16 @@
         <v>99</v>
       </c>
       <c r="N93" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O93" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P93" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q93" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R93" s="50" t="s">
         <v>196</v>
@@ -13310,7 +13307,7 @@
         <v>292</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D94" s="36" t="s">
         <v>381</v>
@@ -13343,16 +13340,16 @@
         <v>100</v>
       </c>
       <c r="N94" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O94" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P94" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q94" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R94" s="50" t="s">
         <v>196</v>
@@ -13381,7 +13378,7 @@
         <v>293</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D95" s="36" t="s">
         <v>381</v>
@@ -13414,16 +13411,16 @@
         <v>101</v>
       </c>
       <c r="N95" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O95" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P95" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q95" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R95" s="50" t="s">
         <v>196</v>
@@ -13452,7 +13449,7 @@
         <v>294</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D96" s="36" t="s">
         <v>381</v>
@@ -13485,16 +13482,16 @@
         <v>102</v>
       </c>
       <c r="N96" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O96" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P96" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q96" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R96" s="50" t="s">
         <v>196</v>
@@ -13523,7 +13520,7 @@
         <v>295</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D97" s="36" t="s">
         <v>381</v>
@@ -13556,16 +13553,16 @@
         <v>103</v>
       </c>
       <c r="N97" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O97" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P97" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q97" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R97" s="50" t="s">
         <v>196</v>
@@ -13594,7 +13591,7 @@
         <v>296</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D98" s="36" t="s">
         <v>381</v>
@@ -13627,16 +13624,16 @@
         <v>104</v>
       </c>
       <c r="N98" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O98" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P98" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q98" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R98" s="50" t="s">
         <v>196</v>
@@ -13665,7 +13662,7 @@
         <v>297</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D99" s="36" t="s">
         <v>381</v>
@@ -13698,16 +13695,16 @@
         <v>105</v>
       </c>
       <c r="N99" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O99" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P99" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q99" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R99" s="50" t="s">
         <v>196</v>
@@ -13736,7 +13733,7 @@
         <v>298</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D100" s="36" t="s">
         <v>381</v>
@@ -13769,16 +13766,16 @@
         <v>106</v>
       </c>
       <c r="N100" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O100" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P100" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q100" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R100" s="50" t="s">
         <v>196</v>
@@ -13807,7 +13804,7 @@
         <v>299</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D101" s="36" t="s">
         <v>381</v>
@@ -13840,16 +13837,16 @@
         <v>107</v>
       </c>
       <c r="N101" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O101" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P101" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q101" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R101" s="50" t="s">
         <v>196</v>
@@ -13878,7 +13875,7 @@
         <v>300</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D102" s="36" t="s">
         <v>381</v>
@@ -13911,16 +13908,16 @@
         <v>108</v>
       </c>
       <c r="N102" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O102" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P102" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q102" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R102" s="50" t="s">
         <v>196</v>
@@ -13949,7 +13946,7 @@
         <v>301</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D103" s="36" t="s">
         <v>381</v>
@@ -13982,16 +13979,16 @@
         <v>109</v>
       </c>
       <c r="N103" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O103" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P103" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q103" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R103" s="50" t="s">
         <v>196</v>
@@ -14020,7 +14017,7 @@
         <v>302</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D104" s="36" t="s">
         <v>381</v>
@@ -14053,16 +14050,16 @@
         <v>110</v>
       </c>
       <c r="N104" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O104" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P104" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q104" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R104" s="50" t="s">
         <v>196</v>
@@ -14091,7 +14088,7 @@
         <v>303</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D105" s="36" t="s">
         <v>381</v>
@@ -14124,16 +14121,16 @@
         <v>111</v>
       </c>
       <c r="N105" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O105" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P105" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q105" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R105" s="50" t="s">
         <v>196</v>
@@ -14162,7 +14159,7 @@
         <v>304</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D106" s="36" t="s">
         <v>381</v>
@@ -14195,16 +14192,16 @@
         <v>112</v>
       </c>
       <c r="N106" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O106" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P106" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q106" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R106" s="50" t="s">
         <v>196</v>
@@ -14233,7 +14230,7 @@
         <v>305</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D107" s="36" t="s">
         <v>381</v>
@@ -14266,16 +14263,16 @@
         <v>113</v>
       </c>
       <c r="N107" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O107" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P107" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q107" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R107" s="50" t="s">
         <v>196</v>
@@ -14304,7 +14301,7 @@
         <v>306</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D108" s="36" t="s">
         <v>381</v>
@@ -14337,16 +14334,16 @@
         <v>114</v>
       </c>
       <c r="N108" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O108" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P108" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q108" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R108" s="50" t="s">
         <v>196</v>
@@ -14375,7 +14372,7 @@
         <v>307</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D109" s="36" t="s">
         <v>381</v>
@@ -14408,16 +14405,16 @@
         <v>115</v>
       </c>
       <c r="N109" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O109" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P109" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q109" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R109" s="50" t="s">
         <v>196</v>
@@ -14446,7 +14443,7 @@
         <v>308</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D110" s="36" t="s">
         <v>381</v>
@@ -14479,16 +14476,16 @@
         <v>116</v>
       </c>
       <c r="N110" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O110" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P110" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q110" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R110" s="50" t="s">
         <v>196</v>
@@ -14517,7 +14514,7 @@
         <v>309</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D111" s="36" t="s">
         <v>381</v>
@@ -14550,16 +14547,16 @@
         <v>117</v>
       </c>
       <c r="N111" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O111" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P111" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q111" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R111" s="50" t="s">
         <v>196</v>
@@ -14588,7 +14585,7 @@
         <v>310</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D112" s="36" t="s">
         <v>381</v>
@@ -14621,16 +14618,16 @@
         <v>119</v>
       </c>
       <c r="N112" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O112" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P112" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q112" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R112" s="50" t="s">
         <v>196</v>
@@ -14659,7 +14656,7 @@
         <v>311</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D113" s="36" t="s">
         <v>381</v>
@@ -14692,16 +14689,16 @@
         <v>120</v>
       </c>
       <c r="N113" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O113" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P113" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q113" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R113" s="50" t="s">
         <v>196</v>
@@ -14730,7 +14727,7 @@
         <v>312</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D114" s="36" t="s">
         <v>381</v>
@@ -14763,16 +14760,16 @@
         <v>121</v>
       </c>
       <c r="N114" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O114" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P114" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q114" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R114" s="50" t="s">
         <v>196</v>
@@ -14801,7 +14798,7 @@
         <v>313</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D115" s="36" t="s">
         <v>381</v>
@@ -14834,16 +14831,16 @@
         <v>122</v>
       </c>
       <c r="N115" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O115" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P115" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q115" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R115" s="50" t="s">
         <v>196</v>
@@ -14872,7 +14869,7 @@
         <v>314</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D116" s="36" t="s">
         <v>381</v>
@@ -14905,16 +14902,16 @@
         <v>123</v>
       </c>
       <c r="N116" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O116" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P116" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q116" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R116" s="50" t="s">
         <v>196</v>
@@ -14943,7 +14940,7 @@
         <v>315</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D117" s="36" t="s">
         <v>381</v>
@@ -14976,16 +14973,16 @@
         <v>124</v>
       </c>
       <c r="N117" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O117" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P117" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q117" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R117" s="50" t="s">
         <v>196</v>
@@ -15014,7 +15011,7 @@
         <v>316</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D118" s="36" t="s">
         <v>381</v>
@@ -15047,16 +15044,16 @@
         <v>125</v>
       </c>
       <c r="N118" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O118" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P118" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q118" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R118" s="50" t="s">
         <v>196</v>
@@ -15085,7 +15082,7 @@
         <v>317</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D119" s="36" t="s">
         <v>381</v>
@@ -15118,16 +15115,16 @@
         <v>126</v>
       </c>
       <c r="N119" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O119" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P119" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q119" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R119" s="50" t="s">
         <v>196</v>
@@ -15156,7 +15153,7 @@
         <v>318</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D120" s="36" t="s">
         <v>381</v>
@@ -15189,16 +15186,16 @@
         <v>127</v>
       </c>
       <c r="N120" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O120" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P120" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q120" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R120" s="50" t="s">
         <v>196</v>
@@ -15227,7 +15224,7 @@
         <v>319</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D121" s="36" t="s">
         <v>381</v>
@@ -15260,16 +15257,16 @@
         <v>128</v>
       </c>
       <c r="N121" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O121" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P121" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q121" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R121" s="50" t="s">
         <v>196</v>
@@ -15298,7 +15295,7 @@
         <v>320</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D122" s="36" t="s">
         <v>381</v>
@@ -15331,16 +15328,16 @@
         <v>129</v>
       </c>
       <c r="N122" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O122" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P122" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q122" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R122" s="50" t="s">
         <v>196</v>
@@ -15369,7 +15366,7 @@
         <v>321</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D123" s="36" t="s">
         <v>381</v>
@@ -15402,16 +15399,16 @@
         <v>130</v>
       </c>
       <c r="N123" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O123" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P123" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q123" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R123" s="50" t="s">
         <v>196</v>
@@ -15437,10 +15434,10 @@
         <v>124</v>
       </c>
       <c r="B124" s="14" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D124" s="36" t="s">
         <v>381</v>
@@ -15473,16 +15470,16 @@
         <v>131</v>
       </c>
       <c r="N124" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O124" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P124" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q124" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R124" s="50" t="s">
         <v>196</v>
@@ -15508,10 +15505,10 @@
         <v>125</v>
       </c>
       <c r="B125" s="14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D125" s="36" t="s">
         <v>381</v>
@@ -15544,16 +15541,16 @@
         <v>118</v>
       </c>
       <c r="N125" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O125" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P125" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q125" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R125" s="50" t="s">
         <v>196</v>
@@ -15582,7 +15579,7 @@
         <v>322</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D126" s="36" t="s">
         <v>381</v>
@@ -15615,16 +15612,16 @@
         <v>132</v>
       </c>
       <c r="N126" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O126" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P126" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q126" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R126" s="50" t="s">
         <v>196</v>
@@ -15653,7 +15650,7 @@
         <v>323</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D127" s="36" t="s">
         <v>381</v>
@@ -15686,16 +15683,16 @@
         <v>133</v>
       </c>
       <c r="N127" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O127" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P127" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q127" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R127" s="50" t="s">
         <v>196</v>
@@ -15724,7 +15721,7 @@
         <v>324</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D128" s="36" t="s">
         <v>381</v>
@@ -15757,16 +15754,16 @@
         <v>134</v>
       </c>
       <c r="N128" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O128" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P128" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q128" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R128" s="50" t="s">
         <v>196</v>
@@ -15795,7 +15792,7 @@
         <v>325</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D129" s="36" t="s">
         <v>381</v>
@@ -15828,16 +15825,16 @@
         <v>135</v>
       </c>
       <c r="N129" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O129" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P129" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q129" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R129" s="50" t="s">
         <v>196</v>
@@ -15866,7 +15863,7 @@
         <v>326</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D130" s="36" t="s">
         <v>381</v>
@@ -15899,16 +15896,16 @@
         <v>136</v>
       </c>
       <c r="N130" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O130" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P130" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q130" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R130" s="50" t="s">
         <v>196</v>
@@ -15937,7 +15934,7 @@
         <v>327</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D131" s="36" t="s">
         <v>381</v>
@@ -15970,16 +15967,16 @@
         <v>137</v>
       </c>
       <c r="N131" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O131" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P131" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q131" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R131" s="50" t="s">
         <v>196</v>
@@ -16008,7 +16005,7 @@
         <v>328</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D132" s="36" t="s">
         <v>381</v>
@@ -16041,16 +16038,16 @@
         <v>138</v>
       </c>
       <c r="N132" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O132" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P132" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q132" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R132" s="50" t="s">
         <v>196</v>
@@ -16079,7 +16076,7 @@
         <v>329</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D133" s="36" t="s">
         <v>381</v>
@@ -16109,19 +16106,19 @@
         <v>1</v>
       </c>
       <c r="M133" s="11" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="N133" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O133" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P133" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q133" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R133" s="50" t="s">
         <v>196</v>
@@ -16150,7 +16147,7 @@
         <v>330</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D134" s="36" t="s">
         <v>381</v>
@@ -16180,19 +16177,19 @@
         <v>1</v>
       </c>
       <c r="M134" s="11" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="N134" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O134" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P134" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q134" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R134" s="50" t="s">
         <v>196</v>
@@ -16221,7 +16218,7 @@
         <v>331</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D135" s="36" t="s">
         <v>381</v>
@@ -16251,19 +16248,19 @@
         <v>1</v>
       </c>
       <c r="M135" s="11" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N135" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O135" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P135" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q135" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R135" s="50" t="s">
         <v>196</v>
@@ -16292,7 +16289,7 @@
         <v>332</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D136" s="36" t="s">
         <v>381</v>
@@ -16322,19 +16319,19 @@
         <v>1</v>
       </c>
       <c r="M136" s="11" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="N136" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O136" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P136" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q136" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R136" s="50" t="s">
         <v>196</v>
@@ -16363,7 +16360,7 @@
         <v>333</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D137" s="36" t="s">
         <v>381</v>
@@ -16393,19 +16390,19 @@
         <v>1</v>
       </c>
       <c r="M137" s="11" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="N137" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O137" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P137" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q137" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R137" s="50" t="s">
         <v>196</v>
@@ -16434,7 +16431,7 @@
         <v>334</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D138" s="36" t="s">
         <v>381</v>
@@ -16467,16 +16464,16 @@
         <v>139</v>
       </c>
       <c r="N138" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O138" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P138" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q138" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R138" s="50" t="s">
         <v>196</v>
@@ -16505,7 +16502,7 @@
         <v>335</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D139" s="36" t="s">
         <v>381</v>
@@ -16538,16 +16535,16 @@
         <v>140</v>
       </c>
       <c r="N139" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O139" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P139" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q139" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R139" s="50" t="s">
         <v>196</v>
@@ -16576,7 +16573,7 @@
         <v>336</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D140" s="36" t="s">
         <v>381</v>
@@ -16609,16 +16606,16 @@
         <v>141</v>
       </c>
       <c r="N140" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O140" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P140" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q140" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R140" s="50" t="s">
         <v>196</v>
@@ -16647,7 +16644,7 @@
         <v>337</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D141" s="36" t="s">
         <v>381</v>
@@ -16680,16 +16677,16 @@
         <v>142</v>
       </c>
       <c r="N141" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O141" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P141" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q141" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R141" s="50" t="s">
         <v>196</v>
@@ -16718,7 +16715,7 @@
         <v>338</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D142" s="36" t="s">
         <v>381</v>
@@ -16751,16 +16748,16 @@
         <v>143</v>
       </c>
       <c r="N142" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O142" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P142" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q142" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R142" s="50" t="s">
         <v>196</v>
@@ -16789,7 +16786,7 @@
         <v>339</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D143" s="36" t="s">
         <v>381</v>
@@ -16822,16 +16819,16 @@
         <v>144</v>
       </c>
       <c r="N143" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O143" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P143" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q143" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R143" s="50" t="s">
         <v>196</v>
@@ -16860,7 +16857,7 @@
         <v>340</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D144" s="36" t="s">
         <v>381</v>
@@ -16893,16 +16890,16 @@
         <v>145</v>
       </c>
       <c r="N144" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O144" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P144" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q144" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R144" s="50" t="s">
         <v>196</v>
@@ -16931,7 +16928,7 @@
         <v>341</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D145" s="36" t="s">
         <v>381</v>
@@ -16964,16 +16961,16 @@
         <v>146</v>
       </c>
       <c r="N145" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O145" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P145" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q145" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R145" s="50" t="s">
         <v>196</v>
@@ -17002,7 +16999,7 @@
         <v>342</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D146" s="36" t="s">
         <v>381</v>
@@ -17035,16 +17032,16 @@
         <v>147</v>
       </c>
       <c r="N146" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O146" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P146" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q146" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R146" s="50" t="s">
         <v>196</v>
@@ -17073,7 +17070,7 @@
         <v>343</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D147" s="36" t="s">
         <v>381</v>
@@ -17106,16 +17103,16 @@
         <v>148</v>
       </c>
       <c r="N147" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O147" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P147" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q147" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R147" s="50" t="s">
         <v>196</v>
@@ -17144,7 +17141,7 @@
         <v>344</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D148" s="36" t="s">
         <v>381</v>
@@ -17177,16 +17174,16 @@
         <v>149</v>
       </c>
       <c r="N148" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O148" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P148" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q148" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R148" s="50" t="s">
         <v>196</v>
@@ -17215,7 +17212,7 @@
         <v>345</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D149" s="36" t="s">
         <v>381</v>
@@ -17248,16 +17245,16 @@
         <v>150</v>
       </c>
       <c r="N149" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O149" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P149" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q149" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R149" s="50" t="s">
         <v>196</v>
@@ -17286,7 +17283,7 @@
         <v>346</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D150" s="36" t="s">
         <v>381</v>
@@ -17319,16 +17316,16 @@
         <v>151</v>
       </c>
       <c r="N150" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O150" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P150" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q150" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R150" s="50" t="s">
         <v>196</v>
@@ -17357,7 +17354,7 @@
         <v>347</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D151" s="36" t="s">
         <v>381</v>
@@ -17390,16 +17387,16 @@
         <v>152</v>
       </c>
       <c r="N151" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O151" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P151" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q151" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R151" s="50" t="s">
         <v>196</v>
@@ -17428,7 +17425,7 @@
         <v>348</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D152" s="36" t="s">
         <v>381</v>
@@ -17461,16 +17458,16 @@
         <v>153</v>
       </c>
       <c r="N152" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O152" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P152" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q152" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R152" s="50" t="s">
         <v>196</v>
@@ -17499,7 +17496,7 @@
         <v>349</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D153" s="36" t="s">
         <v>381</v>
@@ -17532,16 +17529,16 @@
         <v>154</v>
       </c>
       <c r="N153" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O153" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P153" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q153" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R153" s="50" t="s">
         <v>196</v>
@@ -17570,7 +17567,7 @@
         <v>350</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D154" s="36" t="s">
         <v>381</v>
@@ -17600,19 +17597,19 @@
         <v>1</v>
       </c>
       <c r="M154" s="11" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="N154" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O154" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P154" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q154" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R154" s="50" t="s">
         <v>196</v>
@@ -17641,7 +17638,7 @@
         <v>351</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D155" s="36" t="s">
         <v>381</v>
@@ -17674,16 +17671,16 @@
         <v>155</v>
       </c>
       <c r="N155" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O155" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P155" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q155" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R155" s="50" t="s">
         <v>196</v>
@@ -17712,7 +17709,7 @@
         <v>352</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D156" s="36" t="s">
         <v>381</v>
@@ -17745,16 +17742,16 @@
         <v>156</v>
       </c>
       <c r="N156" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O156" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P156" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q156" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R156" s="50" t="s">
         <v>196</v>
@@ -17783,7 +17780,7 @@
         <v>353</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D157" s="36" t="s">
         <v>381</v>
@@ -17816,16 +17813,16 @@
         <v>157</v>
       </c>
       <c r="N157" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O157" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P157" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q157" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R157" s="50" t="s">
         <v>196</v>
@@ -17854,7 +17851,7 @@
         <v>354</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D158" s="36" t="s">
         <v>381</v>
@@ -17887,16 +17884,16 @@
         <v>158</v>
       </c>
       <c r="N158" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O158" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P158" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q158" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R158" s="50" t="s">
         <v>196</v>
@@ -17925,7 +17922,7 @@
         <v>355</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D159" s="36" t="s">
         <v>381</v>
@@ -17958,16 +17955,16 @@
         <v>159</v>
       </c>
       <c r="N159" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O159" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P159" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q159" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R159" s="50" t="s">
         <v>196</v>
@@ -17996,7 +17993,7 @@
         <v>356</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D160" s="36" t="s">
         <v>381</v>
@@ -18029,16 +18026,16 @@
         <v>160</v>
       </c>
       <c r="N160" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O160" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P160" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q160" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R160" s="50" t="s">
         <v>196</v>
@@ -18067,7 +18064,7 @@
         <v>357</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D161" s="36" t="s">
         <v>381</v>
@@ -18100,16 +18097,16 @@
         <v>161</v>
       </c>
       <c r="N161" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O161" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P161" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q161" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R161" s="50" t="s">
         <v>196</v>
@@ -18138,7 +18135,7 @@
         <v>358</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D162" s="36" t="s">
         <v>381</v>
@@ -18171,16 +18168,16 @@
         <v>162</v>
       </c>
       <c r="N162" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O162" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P162" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q162" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R162" s="50" t="s">
         <v>196</v>
@@ -18209,7 +18206,7 @@
         <v>359</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D163" s="36" t="s">
         <v>381</v>
@@ -18242,16 +18239,16 @@
         <v>163</v>
       </c>
       <c r="N163" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O163" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P163" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q163" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R163" s="50" t="s">
         <v>196</v>
@@ -18280,7 +18277,7 @@
         <v>360</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D164" s="36" t="s">
         <v>381</v>
@@ -18313,16 +18310,16 @@
         <v>164</v>
       </c>
       <c r="N164" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O164" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P164" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q164" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R164" s="50" t="s">
         <v>196</v>
@@ -18351,7 +18348,7 @@
         <v>361</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D165" s="36" t="s">
         <v>381</v>
@@ -18384,16 +18381,16 @@
         <v>165</v>
       </c>
       <c r="N165" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O165" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P165" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q165" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R165" s="50" t="s">
         <v>196</v>
@@ -18422,7 +18419,7 @@
         <v>362</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D166" s="36" t="s">
         <v>381</v>
@@ -18455,16 +18452,16 @@
         <v>166</v>
       </c>
       <c r="N166" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O166" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P166" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q166" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R166" s="50" t="s">
         <v>196</v>
@@ -18493,7 +18490,7 @@
         <v>363</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D167" s="36" t="s">
         <v>381</v>
@@ -18526,16 +18523,16 @@
         <v>167</v>
       </c>
       <c r="N167" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O167" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P167" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q167" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R167" s="50" t="s">
         <v>196</v>
@@ -18564,7 +18561,7 @@
         <v>364</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D168" s="36" t="s">
         <v>381</v>
@@ -18597,16 +18594,16 @@
         <v>168</v>
       </c>
       <c r="N168" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O168" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P168" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q168" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R168" s="50" t="s">
         <v>196</v>
@@ -18635,7 +18632,7 @@
         <v>365</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D169" s="36" t="s">
         <v>381</v>
@@ -18668,16 +18665,16 @@
         <v>169</v>
       </c>
       <c r="N169" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O169" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P169" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q169" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R169" s="50" t="s">
         <v>196</v>
@@ -18706,7 +18703,7 @@
         <v>366</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D170" s="36" t="s">
         <v>381</v>
@@ -18739,16 +18736,16 @@
         <v>170</v>
       </c>
       <c r="N170" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O170" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P170" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q170" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R170" s="50" t="s">
         <v>196</v>
@@ -18777,7 +18774,7 @@
         <v>367</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D171" s="36" t="s">
         <v>381</v>
@@ -18810,16 +18807,16 @@
         <v>171</v>
       </c>
       <c r="N171" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O171" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P171" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q171" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R171" s="50" t="s">
         <v>196</v>
@@ -18848,7 +18845,7 @@
         <v>368</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D172" s="36" t="s">
         <v>381</v>
@@ -18881,16 +18878,16 @@
         <v>172</v>
       </c>
       <c r="N172" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O172" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P172" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q172" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R172" s="50" t="s">
         <v>196</v>
@@ -18919,7 +18916,7 @@
         <v>369</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D173" s="36" t="s">
         <v>381</v>
@@ -18952,16 +18949,16 @@
         <v>173</v>
       </c>
       <c r="N173" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O173" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P173" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q173" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R173" s="50" t="s">
         <v>196</v>
@@ -18990,7 +18987,7 @@
         <v>370</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D174" s="36" t="s">
         <v>381</v>
@@ -19023,16 +19020,16 @@
         <v>174</v>
       </c>
       <c r="N174" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O174" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P174" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q174" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R174" s="50" t="s">
         <v>196</v>
@@ -19061,7 +19058,7 @@
         <v>371</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D175" s="36" t="s">
         <v>381</v>
@@ -19094,16 +19091,16 @@
         <v>175</v>
       </c>
       <c r="N175" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O175" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P175" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q175" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R175" s="50" t="s">
         <v>196</v>
@@ -19132,7 +19129,7 @@
         <v>372</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D176" s="36" t="s">
         <v>381</v>
@@ -19165,16 +19162,16 @@
         <v>176</v>
       </c>
       <c r="N176" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O176" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P176" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q176" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R176" s="50" t="s">
         <v>196</v>
@@ -19203,7 +19200,7 @@
         <v>373</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D177" s="36" t="s">
         <v>381</v>
@@ -19236,16 +19233,16 @@
         <v>177</v>
       </c>
       <c r="N177" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O177" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P177" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q177" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R177" s="50" t="s">
         <v>196</v>
@@ -19274,7 +19271,7 @@
         <v>374</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D178" s="36" t="s">
         <v>381</v>
@@ -19307,16 +19304,16 @@
         <v>178</v>
       </c>
       <c r="N178" s="47" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O178" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="P178" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q178" s="48" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R178" s="50" t="s">
         <v>196</v>
@@ -19347,18 +19344,18 @@
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N2:Q4">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R1 T1 V1 D1 F1 H1 L1 N1 P1">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:W178">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:Q4">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1D.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F7AEDB-F0DC-47D9-BDB4-D691E0926BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -2280,84 +2280,6 @@
     <dxf>
       <font>
         <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor rgb="FFFFDE75"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
@@ -2468,84 +2390,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor rgb="FFFFDE75"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -3927,6 +3771,162 @@
         <vertAlign val="baseline"/>
         <sz val="6"/>
         <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF2CB"/>
+          <bgColor rgb="FFFFDE75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF2CB"/>
+          <bgColor rgb="FFFFDE75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
         <name val="Arial Nova Cond"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -4233,28 +4233,28 @@
     <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="62" dataDxfId="61"/>
     <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="60" dataDxfId="59"/>
     <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="1" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="16" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="32" dataDxfId="31"/>
-    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="30" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="28" dataDxfId="27"/>
-    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="26" dataDxfId="25"/>
-    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="24" dataDxfId="23"/>
-    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="22" dataDxfId="21"/>
-    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="20" dataDxfId="19"/>
-    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="18" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="30" dataDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="28" dataDxfId="27"/>
+    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="26" dataDxfId="25"/>
+    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="24" dataDxfId="23"/>
+    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="22" dataDxfId="21"/>
+    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="20" dataDxfId="19"/>
+    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="18" dataDxfId="17"/>
+    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="16" dataDxfId="15"/>
+    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="14" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4579,14 +4579,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E43746A7-9034-4253-BBC7-A96C5E7ADA0F}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="8.65" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>182</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>183</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>9</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>184</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>188</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>189</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>190</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>191</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -4775,19 +4775,19 @@
         <v>452</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>192</v>
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46148.629343055552</v>
+        <v>46157.684288657409</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>460</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>456</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="41" t="s">
         <v>461</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>181</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>193</v>
       </c>
@@ -4844,7 +4844,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>199</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>201</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>448</v>
       </c>
@@ -4886,25 +4886,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E9646D-6465-47E5-AFCE-470E9864FE33}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA19"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="6.83203125" style="33" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="33" customWidth="1"/>
-    <col min="7" max="11" width="8.6640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="6.796875" style="33" customWidth="1"/>
+    <col min="6" max="6" width="12.69921875" style="33" customWidth="1"/>
+    <col min="7" max="11" width="8.69921875" style="33" bestFit="1" customWidth="1"/>
     <col min="12" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="42.6640625" customWidth="1"/>
+    <col min="16" max="16" width="42.69921875" customWidth="1"/>
     <col min="17" max="17" width="44.5" customWidth="1"/>
-    <col min="18" max="18" width="5.83203125" customWidth="1"/>
+    <col min="18" max="18" width="5.796875" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="6.6640625" customWidth="1"/>
-    <col min="21" max="21" width="5.83203125" customWidth="1"/>
-    <col min="22" max="22" width="8.1640625" customWidth="1"/>
-    <col min="23" max="23" width="8.6640625" customWidth="1"/>
-    <col min="27" max="27" width="79.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.69921875" customWidth="1"/>
+    <col min="21" max="21" width="5.796875" customWidth="1"/>
+    <col min="22" max="22" width="8.19921875" customWidth="1"/>
+    <col min="23" max="23" width="8.69921875" customWidth="1"/>
+    <col min="27" max="27" width="79.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="30.9" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>385</v>
       </c>
@@ -4987,7 +4987,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="52">
         <v>2</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="52">
         <v>3</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="52">
         <v>4</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="52">
         <v>5</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="52">
         <v>6</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="52">
         <v>7</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="52">
         <v>8</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52">
         <v>9</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="52">
         <v>10</v>
       </c>
@@ -5806,7 +5806,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="52">
         <v>11</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="52">
         <v>12</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="52">
         <v>13</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="52">
         <v>14</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="52">
         <v>15</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="52">
         <v>16</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="52">
         <v>17</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52">
         <v>18</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="52">
         <v>19</v>
       </c>
@@ -6627,18 +6627,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A19">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA19">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6653,13 +6653,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E7274B-2192-4DC4-A644-E1AD662613FF}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>408</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="26">
         <v>2</v>
       </c>
@@ -6791,7 +6791,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6806,13 +6806,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA41B1A8-F6C2-4E23-9DBE-2B95F8FB901A}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.83203125" customWidth="1"/>
+    <col min="2" max="3" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="29">
         <v>1</v>
       </c>
@@ -6823,7 +6823,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="25">
         <v>2</v>
       </c>
@@ -6836,7 +6836,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6848,35 +6848,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02829C2B-674F-4380-82F9-2448D015A8F3}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A1:Y178"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="41.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.296875" customWidth="1"/>
+    <col min="3" max="4" width="8.296875" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.69921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="41.296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.69921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.69921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>194</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="45">
         <v>2</v>
       </c>
@@ -7030,7 +7030,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="45">
         <v>3</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="45">
         <v>4</v>
       </c>
@@ -7184,7 +7184,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="45">
         <v>5</v>
       </c>
@@ -7261,7 +7261,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="45">
         <v>6</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="45">
         <v>7</v>
       </c>
@@ -7415,7 +7415,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="45">
         <v>8</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="45">
         <v>9</v>
       </c>
@@ -7569,7 +7569,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="45">
         <v>10</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="45">
         <v>11</v>
       </c>
@@ -7723,7 +7723,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="45">
         <v>12</v>
       </c>
@@ -7800,7 +7800,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="45">
         <v>13</v>
       </c>
@@ -7877,7 +7877,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="45">
         <v>14</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="45">
         <v>15</v>
       </c>
@@ -8031,7 +8031,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="45">
         <v>16</v>
       </c>
@@ -8108,7 +8108,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="45">
         <v>17</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="45">
         <v>18</v>
       </c>
@@ -8262,7 +8262,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="45">
         <v>19</v>
       </c>
@@ -8339,7 +8339,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="45">
         <v>20</v>
       </c>
@@ -8416,7 +8416,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="45">
         <v>21</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="45">
         <v>22</v>
       </c>
@@ -8570,7 +8570,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="45">
         <v>23</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="45">
         <v>24</v>
       </c>
@@ -8724,7 +8724,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="45">
         <v>25</v>
       </c>
@@ -8801,7 +8801,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="45">
         <v>26</v>
       </c>
@@ -8878,7 +8878,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="45">
         <v>27</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="45">
         <v>28</v>
       </c>
@@ -9032,7 +9032,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="45">
         <v>29</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="45">
         <v>30</v>
       </c>
@@ -9186,7 +9186,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="45">
         <v>31</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="45">
         <v>32</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="45">
         <v>33</v>
       </c>
@@ -9417,7 +9417,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="45">
         <v>34</v>
       </c>
@@ -9494,7 +9494,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="45">
         <v>35</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="45">
         <v>36</v>
       </c>
@@ -9648,7 +9648,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="45">
         <v>37</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="45">
         <v>38</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="45">
         <v>39</v>
       </c>
@@ -9879,7 +9879,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="45">
         <v>40</v>
       </c>
@@ -9956,7 +9956,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="45">
         <v>41</v>
       </c>
@@ -10033,7 +10033,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="45">
         <v>42</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="45">
         <v>43</v>
       </c>
@@ -10187,7 +10187,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="45">
         <v>44</v>
       </c>
@@ -10264,7 +10264,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="45">
         <v>45</v>
       </c>
@@ -10341,7 +10341,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="45">
         <v>46</v>
       </c>
@@ -10418,7 +10418,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="45">
         <v>47</v>
       </c>
@@ -10495,7 +10495,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="45">
         <v>48</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="45">
         <v>49</v>
       </c>
@@ -10649,7 +10649,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="45">
         <v>50</v>
       </c>
@@ -10726,7 +10726,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="45">
         <v>51</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="45">
         <v>52</v>
       </c>
@@ -10880,7 +10880,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="45">
         <v>53</v>
       </c>
@@ -10957,7 +10957,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="45">
         <v>54</v>
       </c>
@@ -11034,7 +11034,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="45">
         <v>55</v>
       </c>
@@ -11111,7 +11111,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="45">
         <v>56</v>
       </c>
@@ -11188,7 +11188,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="45">
         <v>57</v>
       </c>
@@ -11265,7 +11265,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="45">
         <v>58</v>
       </c>
@@ -11342,7 +11342,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="45">
         <v>59</v>
       </c>
@@ -11419,7 +11419,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="45">
         <v>60</v>
       </c>
@@ -11496,7 +11496,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="45">
         <v>61</v>
       </c>
@@ -11573,7 +11573,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="45">
         <v>62</v>
       </c>
@@ -11650,7 +11650,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="45">
         <v>63</v>
       </c>
@@ -11727,7 +11727,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="45">
         <v>64</v>
       </c>
@@ -11804,7 +11804,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="45">
         <v>65</v>
       </c>
@@ -11881,7 +11881,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="45">
         <v>66</v>
       </c>
@@ -11958,7 +11958,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="45">
         <v>67</v>
       </c>
@@ -12035,7 +12035,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="45">
         <v>68</v>
       </c>
@@ -12112,7 +12112,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="45">
         <v>69</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="45">
         <v>70</v>
       </c>
@@ -12266,7 +12266,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="45">
         <v>71</v>
       </c>
@@ -12343,7 +12343,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="45">
         <v>72</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="45">
         <v>73</v>
       </c>
@@ -12497,7 +12497,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="45">
         <v>74</v>
       </c>
@@ -12574,7 +12574,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="45">
         <v>75</v>
       </c>
@@ -12651,7 +12651,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="45">
         <v>76</v>
       </c>
@@ -12728,7 +12728,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="45">
         <v>77</v>
       </c>
@@ -12805,7 +12805,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="45">
         <v>78</v>
       </c>
@@ -12882,7 +12882,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="45">
         <v>79</v>
       </c>
@@ -12959,7 +12959,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="45">
         <v>80</v>
       </c>
@@ -13036,7 +13036,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="45">
         <v>81</v>
       </c>
@@ -13113,7 +13113,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="45">
         <v>82</v>
       </c>
@@ -13190,7 +13190,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="45">
         <v>83</v>
       </c>
@@ -13267,7 +13267,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="45">
         <v>84</v>
       </c>
@@ -13344,7 +13344,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="45">
         <v>85</v>
       </c>
@@ -13421,7 +13421,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="45">
         <v>86</v>
       </c>
@@ -13498,7 +13498,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="45">
         <v>87</v>
       </c>
@@ -13575,7 +13575,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="45">
         <v>88</v>
       </c>
@@ -13652,7 +13652,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="45">
         <v>89</v>
       </c>
@@ -13729,7 +13729,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="45">
         <v>90</v>
       </c>
@@ -13806,7 +13806,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="45">
         <v>91</v>
       </c>
@@ -13883,7 +13883,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="45">
         <v>92</v>
       </c>
@@ -13960,7 +13960,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="45">
         <v>93</v>
       </c>
@@ -14037,7 +14037,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="45">
         <v>94</v>
       </c>
@@ -14114,7 +14114,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="45">
         <v>95</v>
       </c>
@@ -14191,7 +14191,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="45">
         <v>96</v>
       </c>
@@ -14268,7 +14268,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="45">
         <v>97</v>
       </c>
@@ -14345,7 +14345,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="45">
         <v>98</v>
       </c>
@@ -14422,7 +14422,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="45">
         <v>99</v>
       </c>
@@ -14499,7 +14499,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="45">
         <v>100</v>
       </c>
@@ -14576,7 +14576,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="45">
         <v>101</v>
       </c>
@@ -14653,7 +14653,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="45">
         <v>102</v>
       </c>
@@ -14730,7 +14730,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="45">
         <v>103</v>
       </c>
@@ -14807,7 +14807,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="45">
         <v>104</v>
       </c>
@@ -14884,7 +14884,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="45">
         <v>105</v>
       </c>
@@ -14961,7 +14961,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="45">
         <v>106</v>
       </c>
@@ -15038,7 +15038,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="45">
         <v>107</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="45">
         <v>108</v>
       </c>
@@ -15192,7 +15192,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="45">
         <v>109</v>
       </c>
@@ -15269,7 +15269,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="45">
         <v>110</v>
       </c>
@@ -15346,7 +15346,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="45">
         <v>111</v>
       </c>
@@ -15423,7 +15423,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="45">
         <v>112</v>
       </c>
@@ -15500,7 +15500,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="45">
         <v>113</v>
       </c>
@@ -15577,7 +15577,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="45">
         <v>114</v>
       </c>
@@ -15654,7 +15654,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="45">
         <v>115</v>
       </c>
@@ -15731,7 +15731,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="45">
         <v>116</v>
       </c>
@@ -15808,7 +15808,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="45">
         <v>117</v>
       </c>
@@ -15885,7 +15885,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="45">
         <v>118</v>
       </c>
@@ -15962,7 +15962,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="45">
         <v>119</v>
       </c>
@@ -16039,7 +16039,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="45">
         <v>120</v>
       </c>
@@ -16116,7 +16116,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="45">
         <v>121</v>
       </c>
@@ -16193,7 +16193,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="45">
         <v>122</v>
       </c>
@@ -16270,7 +16270,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="45">
         <v>123</v>
       </c>
@@ -16347,7 +16347,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="45">
         <v>124</v>
       </c>
@@ -16424,7 +16424,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="45">
         <v>125</v>
       </c>
@@ -16501,7 +16501,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="45">
         <v>126</v>
       </c>
@@ -16578,7 +16578,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="45">
         <v>127</v>
       </c>
@@ -16655,7 +16655,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="45">
         <v>128</v>
       </c>
@@ -16732,7 +16732,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="45">
         <v>129</v>
       </c>
@@ -16809,7 +16809,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="45">
         <v>130</v>
       </c>
@@ -16886,7 +16886,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="45">
         <v>131</v>
       </c>
@@ -16963,7 +16963,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="45">
         <v>132</v>
       </c>
@@ -17040,7 +17040,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="45">
         <v>133</v>
       </c>
@@ -17117,7 +17117,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="45">
         <v>134</v>
       </c>
@@ -17194,7 +17194,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="45">
         <v>135</v>
       </c>
@@ -17271,7 +17271,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="45">
         <v>136</v>
       </c>
@@ -17348,7 +17348,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="45">
         <v>137</v>
       </c>
@@ -17425,7 +17425,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="45">
         <v>138</v>
       </c>
@@ -17502,7 +17502,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="45">
         <v>139</v>
       </c>
@@ -17579,7 +17579,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="45">
         <v>140</v>
       </c>
@@ -17656,7 +17656,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="45">
         <v>141</v>
       </c>
@@ -17733,7 +17733,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="45">
         <v>142</v>
       </c>
@@ -17810,7 +17810,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="45">
         <v>143</v>
       </c>
@@ -17887,7 +17887,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="45">
         <v>144</v>
       </c>
@@ -17964,7 +17964,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="45">
         <v>145</v>
       </c>
@@ -18041,7 +18041,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="45">
         <v>146</v>
       </c>
@@ -18118,7 +18118,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="45">
         <v>147</v>
       </c>
@@ -18195,7 +18195,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="45">
         <v>148</v>
       </c>
@@ -18272,7 +18272,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="45">
         <v>149</v>
       </c>
@@ -18349,7 +18349,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="45">
         <v>150</v>
       </c>
@@ -18426,7 +18426,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="45">
         <v>151</v>
       </c>
@@ -18503,7 +18503,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="45">
         <v>152</v>
       </c>
@@ -18580,7 +18580,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="45">
         <v>153</v>
       </c>
@@ -18657,7 +18657,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="45">
         <v>154</v>
       </c>
@@ -18734,7 +18734,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="45">
         <v>155</v>
       </c>
@@ -18811,7 +18811,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="45">
         <v>156</v>
       </c>
@@ -18888,7 +18888,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="45">
         <v>157</v>
       </c>
@@ -18965,7 +18965,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="45">
         <v>158</v>
       </c>
@@ -19042,7 +19042,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="45">
         <v>159</v>
       </c>
@@ -19119,7 +19119,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="45">
         <v>160</v>
       </c>
@@ -19196,7 +19196,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="45">
         <v>161</v>
       </c>
@@ -19273,7 +19273,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="45">
         <v>162</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="45">
         <v>163</v>
       </c>
@@ -19427,7 +19427,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="45">
         <v>164</v>
       </c>
@@ -19504,7 +19504,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="45">
         <v>165</v>
       </c>
@@ -19581,7 +19581,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="45">
         <v>166</v>
       </c>
@@ -19658,7 +19658,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="45">
         <v>167</v>
       </c>
@@ -19735,7 +19735,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="45">
         <v>168</v>
       </c>
@@ -19812,7 +19812,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="45">
         <v>169</v>
       </c>
@@ -19889,7 +19889,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="45">
         <v>170</v>
       </c>
@@ -19966,7 +19966,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="45">
         <v>171</v>
       </c>
@@ -20043,7 +20043,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="45">
         <v>172</v>
       </c>
@@ -20120,7 +20120,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="45">
         <v>173</v>
       </c>
@@ -20197,7 +20197,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="45">
         <v>174</v>
       </c>
@@ -20274,7 +20274,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="45">
         <v>175</v>
       </c>
@@ -20351,7 +20351,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="45">
         <v>176</v>
       </c>
@@ -20428,7 +20428,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="45">
         <v>177</v>
       </c>
@@ -20505,7 +20505,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="45">
         <v>178</v>
       </c>
@@ -20585,25 +20585,25 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:S4">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1 V1 X1 F1 H1 J1 N1 P1 R1">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y178">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1D.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20084FBA-CCAC-4DCC-BBC9-A266AEB76368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46167.410562962963</v>
+        <v>46214.346835763892</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>449</v>

--- a/Versão5/ABNT/Ontologia_15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590281F8-F2B0-4799-84C3-51DBD73EB375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67FFFE5-7A0A-496D-9730-7A3B3D7C4C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4945" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4945" uniqueCount="597">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1867,9 +1867,6 @@
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>Arquitetura</t>
   </si>
   <si>
     <t>[ 5I ]</t>
@@ -2384,15 +2381,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{DFB85275-A9BE-4413-B02C-324FD368C2A1}"/>
   </cellStyles>
-  <dxfs count="77">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="78">
     <dxf>
       <font>
         <b val="0"/>
@@ -2440,6 +2429,24 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -4428,33 +4435,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:Y178" headerRowCount="0" totalsRowShown="0" headerRowDxfId="76" headerRowBorderDxfId="75" tableBorderDxfId="74" totalsRowBorderDxfId="73">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:Y178" headerRowCount="0" totalsRowShown="0" headerRowDxfId="77" headerRowBorderDxfId="76" tableBorderDxfId="75" totalsRowBorderDxfId="74">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="72" dataDxfId="71"/>
-    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="70" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="68" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="66" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="64" dataDxfId="63"/>
-    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="32" dataDxfId="31"/>
-    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="30" dataDxfId="29"/>
-    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="28" dataDxfId="27"/>
-    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="26" dataDxfId="25"/>
-    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="24" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="73" dataDxfId="72"/>
+    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="71" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="69" dataDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="25" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4981,7 +4988,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46216.267396064817</v>
+        <v>46219.567006249999</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>448</v>
@@ -5086,27 +5093,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E9646D-6465-47E5-AFCE-470E9864FE33}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA32"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.83203125" style="31" customWidth="1"/>
-    <col min="3" max="3" width="6.5" style="31" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" style="31" customWidth="1"/>
-    <col min="5" max="5" width="9.1640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" style="31" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="31" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.6640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" customWidth="1"/>
-    <col min="13" max="13" width="10.5" customWidth="1"/>
-    <col min="14" max="14" width="9.5" customWidth="1"/>
-    <col min="15" max="15" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="58.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="61.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.83203125" style="31" customWidth="1"/>
-    <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="8.1640625" customWidth="1"/>
-    <col min="21" max="21" width="9.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.1640625" customWidth="1"/>
-    <col min="23" max="23" width="8.6640625" style="31" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="75.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="56.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" style="31" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="79.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5193,7 +5203,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="31" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" s="31" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="50">
         <v>2</v>
       </c>
@@ -5265,7 +5275,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="38" t="s">
-        <v>592</v>
+        <v>475</v>
       </c>
       <c r="W2" s="59" t="str">
         <f>CONCATENATE("Key-ABNT-",A2)</f>
@@ -5278,14 +5288,14 @@
         <v>196</v>
       </c>
       <c r="Z2" s="38" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AA2" s="38" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="31" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" s="31" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="50">
         <v>3</v>
       </c>
@@ -5336,7 +5346,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="38" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="Q3" s="38" t="s">
         <v>591</v>
@@ -5357,7 +5367,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="38" t="s">
-        <v>592</v>
+        <v>475</v>
       </c>
       <c r="W3" s="59" t="str">
         <f t="shared" ref="W3:W32" si="4">CONCATENATE("Key-ABNT-",A3)</f>
@@ -5377,7 +5387,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="31" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="31" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="50">
         <v>4</v>
       </c>
@@ -5428,7 +5438,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="38" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="Q4" s="38" t="s">
         <v>591</v>
@@ -5449,7 +5459,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="38" t="s">
-        <v>592</v>
+        <v>475</v>
       </c>
       <c r="W4" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5469,7 +5479,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="31" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" s="31" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="50">
         <v>5</v>
       </c>
@@ -5520,7 +5530,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="Q5" s="38" t="s">
         <v>591</v>
@@ -5541,7 +5551,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="38" t="s">
-        <v>592</v>
+        <v>475</v>
       </c>
       <c r="W5" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5561,7 +5571,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="31" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" s="31" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="50">
         <v>6</v>
       </c>
@@ -5612,7 +5622,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="Q6" s="38" t="s">
         <v>591</v>
@@ -5633,7 +5643,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="38" t="s">
-        <v>592</v>
+        <v>475</v>
       </c>
       <c r="W6" s="59" t="str">
         <f t="shared" si="4"/>
@@ -8046,35 +8056,25 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A32">
-    <cfRule type="cellIs" dxfId="22" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA32">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B32">
+    <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B6 B7:B32">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA1:AA32">
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8227,7 +8227,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8272,7 +8272,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22022,25 +22022,25 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:S4">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1 V1 X1 F1 H1 J1 N1 P1 R1">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y178">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CFDCAE-A563-4F93-8CB5-BE611474D9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE96D00B-A54F-48F8-9A35-7687D5797A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4945" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4984" uniqueCount="629">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1900,13 +1900,91 @@
   </si>
   <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I. Building Information Codes.</t>
+  </si>
+  <si>
+    <t>Fonte1</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>Fonte2</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>Fonte3</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>FonteVegetação1</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>FonteVegetação2</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>FonteVegetação3</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação4</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>FonteVegetação5</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>FonteVegetação6</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação7</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>FonteVegetação8</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>FonteTSB</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>FonteSINAPI</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -1988,8 +2066,34 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2146,6 +2250,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -2208,11 +2318,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2394,38 +2505,31 @@
     <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="16" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{DFB85275-A9BE-4413-B02C-324FD368C2A1}"/>
   </cellStyles>
-  <dxfs count="74">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="72">
     <dxf>
       <font>
         <b val="0"/>
@@ -2491,6 +2595,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4413,33 +4527,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:Y178" headerRowCount="0" totalsRowShown="0" headerRowDxfId="73" headerRowBorderDxfId="72" tableBorderDxfId="71" totalsRowBorderDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69A16A64-3E97-465C-964E-C4C571269A75}" name="Tabla223" displayName="Tabla223" ref="A2:Y178" headerRowCount="0" totalsRowShown="0" headerRowDxfId="71" headerRowBorderDxfId="70" tableBorderDxfId="69" totalsRowBorderDxfId="68">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="69" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="67" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{38E6FF5A-1C06-481D-80DD-C82C301F082C}" name="1" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{3C6C0505-1689-4EE8-8610-376BB44C09BD}" name="Indivíduo" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{9E4249DB-15E5-43EE-8981-0CA7D155306D}" name="Classe" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{06450E5A-D634-468E-85D8-BF532072F033}" name="Coluna2" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{63966EBE-3AE3-4FE5-824F-31F181792B00}" name="Coluna1" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="10" xr3:uid="{B010664B-8605-436F-83C5-07C587B7EBF3}" name="Coluna7" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="11" xr3:uid="{7FFA8EB1-276A-4285-9A7C-A1D18E3DFF8B}" name="Coluna8" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{22CBEBAF-AA10-4617-8459-F68D0C361483}" name="Coluna6" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="8" xr3:uid="{C9056F13-CAD6-42A0-92E3-CCACD5427101}" name="Coluna5" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="15" xr3:uid="{7FF1F7A2-1E10-4F02-A617-405FDDE9D634}" name="Coluna10" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="14" xr3:uid="{A626C0EC-68E3-4B2E-81D7-D867605763EF}" name="Coluna9" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{5A8640B3-3235-4227-88AE-24186B8A867F}" name="Coluna20" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="24" xr3:uid="{7AF5C8AB-6C75-4A72-A612-E8206E08AA62}" name="Coluna19" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="12" xr3:uid="{613D7E6F-53D4-4E84-9337-FF573DD02A33}" name="Fato (11)" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{127ED421-F6A7-4128-8AF7-D3B35A7BF083}" name="Valor8" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{83791CD9-A300-4592-BA84-F1311915870A}" name="Coluna3" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{64784F60-3C84-43BD-A67F-5F0E13177E97}" name="Coluna4" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="16" xr3:uid="{2A7F449A-8617-40F9-A53A-E7F41637FF07}" name="Coluna11" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="17" xr3:uid="{A00A6729-6CD7-45BE-8067-C5D950C77857}" name="Coluna12" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="18" xr3:uid="{38BA47F5-E3A4-4441-811E-FFCE4B66524C}" name="Coluna13" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="19" xr3:uid="{0CD1E3E2-D75C-43AA-B1D7-E6D47E1EA043}" name="Coluna14" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="20" xr3:uid="{C83E6FE7-67F0-4D92-A6EB-2812DDF0E157}" name="Coluna15" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="21" xr3:uid="{691E0314-9C84-4100-A3A1-CCB94C4947BD}" name="Coluna16" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="22" xr3:uid="{DFA507C2-123C-4A86-82E8-279077327DAF}" name="Coluna17" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="23" xr3:uid="{5B916111-DB54-428A-BA8B-06C1A28879DE}" name="Coluna18" headerRowDxfId="19" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4763,7 +4877,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E43746A7-9034-4253-BBC7-A96C5E7ADA0F}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
@@ -4966,7 +5080,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46232.780969097221</v>
+        <v>46233.478236574076</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>447</v>
@@ -5062,7 +5176,157 @@
         <v>449</v>
       </c>
     </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="39" t="s">
+        <v>603</v>
+      </c>
+      <c r="B27" s="61" t="s">
+        <v>604</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="39" t="s">
+        <v>605</v>
+      </c>
+      <c r="B28" s="62" t="s">
+        <v>606</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="39" t="s">
+        <v>607</v>
+      </c>
+      <c r="B29" s="62" t="s">
+        <v>608</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="39" t="s">
+        <v>609</v>
+      </c>
+      <c r="B30" s="63" t="s">
+        <v>610</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="39" t="s">
+        <v>611</v>
+      </c>
+      <c r="B31" s="63" t="s">
+        <v>612</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="39" t="s">
+        <v>613</v>
+      </c>
+      <c r="B32" s="63" t="s">
+        <v>614</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="39" t="s">
+        <v>615</v>
+      </c>
+      <c r="B33" s="65" t="s">
+        <v>616</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="39" t="s">
+        <v>617</v>
+      </c>
+      <c r="B34" s="65" t="s">
+        <v>618</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="39" t="s">
+        <v>619</v>
+      </c>
+      <c r="B35" s="63" t="s">
+        <v>620</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="39" t="s">
+        <v>621</v>
+      </c>
+      <c r="B36" s="65" t="s">
+        <v>622</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="39" t="s">
+        <v>623</v>
+      </c>
+      <c r="B37" s="63" t="s">
+        <v>624</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B38" s="66" t="s">
+        <v>626</v>
+      </c>
+      <c r="C38" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="68" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="39" t="s">
+        <v>627</v>
+      </c>
+      <c r="B39" s="67" t="s">
+        <v>628</v>
+      </c>
+      <c r="C39" s="42" t="s">
+        <v>447</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{AB3C08F0-2812-42D9-8E6A-835D285D3CA0}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{B241F630-284A-4FA7-B290-47037930EB1D}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{37361A8D-7F10-4E7E-B627-688AC0F0F860}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{B9B30222-2EEE-4D09-968A-F563A0CCD1E2}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{5E40CD92-E7D8-482D-B25C-91E7D2C86A49}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -6867,11 +7131,11 @@
         <v>NBR.Temática</v>
       </c>
       <c r="N20" s="52" t="str">
-        <f t="shared" ref="L18:N32" si="10">CONCATENATE("", E20)</f>
+        <f t="shared" ref="N20:N32" si="10">CONCATENATE("", E20)</f>
         <v>NBR.Disciplinas</v>
       </c>
       <c r="O20" s="52" t="str">
-        <f t="shared" ref="O7:O32" si="11">F20</f>
+        <f t="shared" ref="O20:O32" si="11">F20</f>
         <v>NBR.D.Arquitetura</v>
       </c>
       <c r="P20" s="38" t="s">
@@ -6885,7 +7149,7 @@
         <v>196</v>
       </c>
       <c r="S20" s="53" t="str">
-        <f t="shared" ref="S7:U22" si="12">SUBSTITUTE(C20, "_", " ")</f>
+        <f t="shared" ref="S20:U22" si="12">SUBSTITUTE(C20, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T20" s="53" t="str">
@@ -8034,38 +8298,28 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B6 A20:B32">
-    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
+  <conditionalFormatting sqref="A2:B32">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F19">
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6 AA20:AA32">
-    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B19">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F19">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA19">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="AA1:AA32">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8218,7 +8472,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8263,7 +8517,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22013,25 +22267,25 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:S4">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1 V1 X1 F1 H1 J1 N1 P1 R1">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y178">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1D.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE96D00B-A54F-48F8-9A35-7687D5797A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BBD7A8-F197-44A8-AAF9-535FBE2B0E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4984" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4984" uniqueCount="628">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1749,9 +1749,6 @@
     <t>"Disciplinas da Construção"</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
@@ -1776,21 +1773,12 @@
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
   <si>
-    <t>Normativo</t>
-  </si>
-  <si>
-    <t>NBR.Temática</t>
-  </si>
-  <si>
     <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0M. Códigos de Materiais.</t>
   </si>
   <si>
     <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0M. Códigos de materiales.</t>
   </si>
   <si>
-    <t>Interdiciplinar</t>
-  </si>
-  <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0M. Material Codes.</t>
   </si>
   <si>
@@ -1978,6 +1966,15 @@
   </si>
   <si>
     <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>Normativos</t>
+  </si>
+  <si>
+    <t>NBR.Temáticas</t>
   </si>
 </sst>
 </file>
@@ -5080,7 +5077,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46233.478236574076</v>
+        <v>46243.560246412038</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>447</v>
@@ -5178,10 +5175,10 @@
     </row>
     <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B27" s="61" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C27" s="42" t="s">
         <v>447</v>
@@ -5189,10 +5186,10 @@
     </row>
     <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B28" s="62" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C28" s="42" t="s">
         <v>447</v>
@@ -5200,10 +5197,10 @@
     </row>
     <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B29" s="62" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C29" s="42" t="s">
         <v>447</v>
@@ -5211,10 +5208,10 @@
     </row>
     <row r="30" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="39" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B30" s="63" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C30" s="42" t="s">
         <v>447</v>
@@ -5222,10 +5219,10 @@
     </row>
     <row r="31" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="39" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B31" s="63" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C31" s="42" t="s">
         <v>447</v>
@@ -5233,10 +5230,10 @@
     </row>
     <row r="32" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="39" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B32" s="63" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C32" s="42" t="s">
         <v>447</v>
@@ -5244,10 +5241,10 @@
     </row>
     <row r="33" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="39" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B33" s="65" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C33" s="42" t="s">
         <v>447</v>
@@ -5255,10 +5252,10 @@
     </row>
     <row r="34" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="39" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B34" s="65" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C34" s="42" t="s">
         <v>447</v>
@@ -5266,10 +5263,10 @@
     </row>
     <row r="35" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="39" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B35" s="63" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C35" s="42" t="s">
         <v>447</v>
@@ -5277,10 +5274,10 @@
     </row>
     <row r="36" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="39" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B36" s="65" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C36" s="42" t="s">
         <v>447</v>
@@ -5288,10 +5285,10 @@
     </row>
     <row r="37" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="39" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B37" s="63" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C37" s="42" t="s">
         <v>447</v>
@@ -5299,10 +5296,10 @@
     </row>
     <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B38" s="66" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C38" s="42" t="s">
         <v>447</v>
@@ -5310,10 +5307,10 @@
     </row>
     <row r="39" spans="1:3" s="68" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="39" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B39" s="67" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C39" s="42" t="s">
         <v>447</v>
@@ -5335,7 +5332,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E9646D-6465-47E5-AFCE-470E9864FE33}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA32"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="7.85" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.796875" style="31" customWidth="1"/>
@@ -5445,12 +5442,12 @@
         <v>442</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="31" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" s="31" customFormat="1" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="50">
         <v>2</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C2" s="54" t="s">
         <v>471</v>
@@ -5459,7 +5456,7 @@
         <v>473</v>
       </c>
       <c r="E2" s="55" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F2" s="55" t="s">
         <v>472</v>
@@ -5496,10 +5493,10 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="38" t="s">
+        <v>553</v>
+      </c>
+      <c r="Q2" s="38" t="s">
         <v>554</v>
-      </c>
-      <c r="Q2" s="38" t="s">
-        <v>555</v>
       </c>
       <c r="R2" s="38" t="s">
         <v>196</v>
@@ -5530,19 +5527,19 @@
         <v>196</v>
       </c>
       <c r="Z2" s="38" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AA2" s="38" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="31" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" s="31" customFormat="1" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="50">
         <v>3</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C3" s="54" t="s">
         <v>471</v>
@@ -5551,7 +5548,7 @@
         <v>473</v>
       </c>
       <c r="E3" s="55" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F3" s="55" t="s">
         <v>475</v>
@@ -5588,10 +5585,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="38" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Q3" s="38" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="R3" s="38" t="s">
         <v>196</v>
@@ -5629,12 +5626,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="31" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" s="31" customFormat="1" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="50">
         <v>4</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C4" s="54" t="s">
         <v>471</v>
@@ -5643,7 +5640,7 @@
         <v>473</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F4" s="55" t="s">
         <v>476</v>
@@ -5680,10 +5677,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="38" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q4" s="38" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="R4" s="38" t="s">
         <v>196</v>
@@ -5721,12 +5718,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="31" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" s="31" customFormat="1" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="50">
         <v>5</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C5" s="54" t="s">
         <v>471</v>
@@ -5735,7 +5732,7 @@
         <v>473</v>
       </c>
       <c r="E5" s="55" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F5" s="55" t="s">
         <v>477</v>
@@ -5772,10 +5769,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Q5" s="38" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="R5" s="38" t="s">
         <v>196</v>
@@ -5813,12 +5810,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="31" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" s="31" customFormat="1" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="50">
         <v>6</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C6" s="54" t="s">
         <v>471</v>
@@ -5827,7 +5824,7 @@
         <v>473</v>
       </c>
       <c r="E6" s="55" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F6" s="55" t="s">
         <v>478</v>
@@ -5864,10 +5861,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="Q6" s="38" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="R6" s="38" t="s">
         <v>196</v>
@@ -5905,15 +5902,15 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50">
         <v>7</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D7" s="30" t="s">
         <v>407</v>
@@ -5941,7 +5938,7 @@
       </c>
       <c r="L7" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M7" s="52" t="str">
         <f t="shared" si="0"/>
@@ -5956,17 +5953,17 @@
         <v>NBR.0M</v>
       </c>
       <c r="P7" s="52" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="Q7" s="52" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="R7" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S7" s="53" t="str">
         <f t="shared" ref="S7:U19" si="6">SUBSTITUTE(C7, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T7" s="53" t="str">
         <f t="shared" si="6"/>
@@ -5977,7 +5974,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V7" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W7" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5993,18 +5990,18 @@
         <v>479</v>
       </c>
       <c r="AA7" s="56" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50">
         <v>8</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D8" s="30" t="s">
         <v>407</v>
@@ -6032,7 +6029,7 @@
       </c>
       <c r="L8" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M8" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6047,17 +6044,17 @@
         <v>NBR.0P</v>
       </c>
       <c r="P8" s="52" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="Q8" s="52" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="R8" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S8" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T8" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6068,7 +6065,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V8" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W8" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6084,18 +6081,18 @@
         <v>480</v>
       </c>
       <c r="AA8" s="56" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="50">
         <v>9</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>407</v>
@@ -6123,7 +6120,7 @@
       </c>
       <c r="L9" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M9" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6138,17 +6135,17 @@
         <v>NBR.1D</v>
       </c>
       <c r="P9" s="52" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="Q9" s="52" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="R9" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S9" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T9" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6159,7 +6156,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V9" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W9" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6175,18 +6172,18 @@
         <v>377</v>
       </c>
       <c r="AA9" s="56" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50">
         <v>10</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D10" s="30" t="s">
         <v>407</v>
@@ -6214,7 +6211,7 @@
       </c>
       <c r="L10" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M10" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6229,17 +6226,17 @@
         <v>NBR.1F</v>
       </c>
       <c r="P10" s="52" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="Q10" s="52" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="R10" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S10" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T10" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6250,7 +6247,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V10" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W10" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6266,18 +6263,18 @@
         <v>481</v>
       </c>
       <c r="AA10" s="56" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="50">
         <v>11</v>
       </c>
       <c r="B11" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D11" s="30" t="s">
         <v>407</v>
@@ -6305,7 +6302,7 @@
       </c>
       <c r="L11" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M11" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6320,17 +6317,17 @@
         <v>NBR.1S</v>
       </c>
       <c r="P11" s="52" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="Q11" s="52" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="R11" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S11" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T11" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6341,7 +6338,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V11" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W11" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6357,18 +6354,18 @@
         <v>482</v>
       </c>
       <c r="AA11" s="56" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="50">
         <v>12</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D12" s="30" t="s">
         <v>407</v>
@@ -6396,7 +6393,7 @@
       </c>
       <c r="L12" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M12" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6411,17 +6408,17 @@
         <v>NBR.2C</v>
       </c>
       <c r="P12" s="52" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="Q12" s="52" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="R12" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S12" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T12" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6432,7 +6429,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V12" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W12" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6448,18 +6445,18 @@
         <v>483</v>
       </c>
       <c r="AA12" s="56" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="50">
         <v>13</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D13" s="30" t="s">
         <v>407</v>
@@ -6487,7 +6484,7 @@
       </c>
       <c r="L13" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M13" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6502,17 +6499,17 @@
         <v>NBR.2N</v>
       </c>
       <c r="P13" s="52" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="Q13" s="52" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="R13" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S13" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T13" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6523,7 +6520,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V13" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W13" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6539,18 +6536,18 @@
         <v>484</v>
       </c>
       <c r="AA13" s="56" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="50">
         <v>14</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D14" s="30" t="s">
         <v>407</v>
@@ -6578,7 +6575,7 @@
       </c>
       <c r="L14" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M14" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6593,17 +6590,17 @@
         <v>NBR.2Q</v>
       </c>
       <c r="P14" s="52" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="Q14" s="52" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="R14" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S14" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T14" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6614,7 +6611,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V14" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W14" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6630,18 +6627,18 @@
         <v>485</v>
       </c>
       <c r="AA14" s="56" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="50">
         <v>15</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D15" s="30" t="s">
         <v>407</v>
@@ -6669,7 +6666,7 @@
       </c>
       <c r="L15" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M15" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6684,17 +6681,17 @@
         <v>NBR.3E</v>
       </c>
       <c r="P15" s="52" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="Q15" s="52" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="R15" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S15" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T15" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6705,7 +6702,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V15" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W15" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6721,18 +6718,18 @@
         <v>486</v>
       </c>
       <c r="AA15" s="56" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="50">
         <v>16</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D16" s="30" t="s">
         <v>407</v>
@@ -6760,7 +6757,7 @@
       </c>
       <c r="L16" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M16" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6775,17 +6772,17 @@
         <v>NBR.3R</v>
       </c>
       <c r="P16" s="52" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="Q16" s="52" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="R16" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S16" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T16" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6796,7 +6793,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V16" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W16" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6812,18 +6809,18 @@
         <v>487</v>
       </c>
       <c r="AA16" s="56" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="50">
         <v>17</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D17" s="30" t="s">
         <v>407</v>
@@ -6851,7 +6848,7 @@
       </c>
       <c r="L17" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M17" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6866,17 +6863,17 @@
         <v>NBR.4A</v>
       </c>
       <c r="P17" s="52" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="Q17" s="52" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="R17" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S17" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T17" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6887,7 +6884,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V17" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W17" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6903,18 +6900,18 @@
         <v>488</v>
       </c>
       <c r="AA17" s="56" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="50">
         <v>18</v>
       </c>
       <c r="B18" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D18" s="30" t="s">
         <v>407</v>
@@ -6942,7 +6939,7 @@
       </c>
       <c r="L18" s="52" t="str">
         <f t="shared" ref="L18:N19" si="7">CONCATENATE("", C18)</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M18" s="52" t="str">
         <f t="shared" si="7"/>
@@ -6957,17 +6954,17 @@
         <v>NBR.4U</v>
       </c>
       <c r="P18" s="52" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="Q18" s="52" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="R18" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S18" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T18" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6978,7 +6975,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V18" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W18" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6994,18 +6991,18 @@
         <v>489</v>
       </c>
       <c r="AA18" s="56" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="50">
         <v>19</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D19" s="30" t="s">
         <v>407</v>
@@ -7033,7 +7030,7 @@
       </c>
       <c r="L19" s="52" t="str">
         <f t="shared" si="7"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M19" s="52" t="str">
         <f t="shared" si="7"/>
@@ -7048,17 +7045,17 @@
         <v>NBR.5I</v>
       </c>
       <c r="P19" s="52" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="Q19" s="52" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="R19" s="38" t="s">
         <v>196</v>
       </c>
       <c r="S19" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T19" s="53" t="str">
         <f t="shared" si="6"/>
@@ -7069,7 +7066,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V19" s="38" t="s">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="W19" s="59" t="str">
         <f t="shared" si="4"/>
@@ -7085,21 +7082,21 @@
         <v>490</v>
       </c>
       <c r="AA19" s="56" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="50">
         <v>20</v>
       </c>
       <c r="B20" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E20" s="30" t="s">
         <v>548</v>
@@ -7124,11 +7121,11 @@
       </c>
       <c r="L20" s="52" t="str">
         <f t="shared" ref="L20:L32" si="8">CONCATENATE("", C20)</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M20" s="52" t="str">
         <f t="shared" ref="M20:M32" si="9">CONCATENATE("", D20)</f>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N20" s="52" t="str">
         <f t="shared" ref="N20:N32" si="10">CONCATENATE("", E20)</f>
@@ -7150,11 +7147,11 @@
       </c>
       <c r="S20" s="53" t="str">
         <f t="shared" ref="S20:U22" si="12">SUBSTITUTE(C20, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T20" s="53" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U20" s="52" t="str">
         <f t="shared" si="12"/>
@@ -7181,18 +7178,18 @@
         <v>Discipline of Architecture</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="50">
         <v>21</v>
       </c>
       <c r="B21" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E21" s="30" t="s">
         <v>548</v>
@@ -7217,11 +7214,11 @@
       </c>
       <c r="L21" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M21" s="52" t="str">
         <f t="shared" si="9"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N21" s="52" t="str">
         <f t="shared" si="10"/>
@@ -7243,11 +7240,11 @@
       </c>
       <c r="S21" s="53" t="str">
         <f t="shared" si="12"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T21" s="53" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U21" s="52" t="str">
         <f t="shared" si="12"/>
@@ -7274,18 +7271,18 @@
         <v>Construction Discipline</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="50">
         <v>22</v>
       </c>
       <c r="B22" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E22" s="30" t="s">
         <v>548</v>
@@ -7310,11 +7307,11 @@
       </c>
       <c r="L22" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M22" s="52" t="str">
         <f t="shared" si="9"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N22" s="52" t="str">
         <f t="shared" si="10"/>
@@ -7336,11 +7333,11 @@
       </c>
       <c r="S22" s="53" t="str">
         <f t="shared" si="12"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T22" s="53" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U22" s="52" t="str">
         <f t="shared" si="12"/>
@@ -7367,18 +7364,18 @@
         <v>Engineering Discipline</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="50">
         <v>23</v>
       </c>
       <c r="B23" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E23" s="30" t="s">
         <v>548</v>
@@ -7403,11 +7400,11 @@
       </c>
       <c r="L23" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M23" s="52" t="str">
         <f t="shared" si="9"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N23" s="52" t="str">
         <f t="shared" si="10"/>
@@ -7429,11 +7426,11 @@
       </c>
       <c r="S23" s="53" t="str">
         <f t="shared" ref="S23:U32" si="15">SUBSTITUTE(C23, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T23" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U23" s="52" t="str">
         <f t="shared" si="15"/>
@@ -7460,18 +7457,18 @@
         <v>Specialty Discipline</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="50">
         <v>24</v>
       </c>
       <c r="B24" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E24" s="30" t="s">
         <v>548</v>
@@ -7496,11 +7493,11 @@
       </c>
       <c r="L24" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M24" s="52" t="str">
         <f t="shared" si="9"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N24" s="52" t="str">
         <f t="shared" si="10"/>
@@ -7522,11 +7519,11 @@
       </c>
       <c r="S24" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T24" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U24" s="52" t="str">
         <f t="shared" si="15"/>
@@ -7553,18 +7550,18 @@
         <v>Manufacturing Discipline</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="50">
         <v>25</v>
       </c>
       <c r="B25" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E25" s="30" t="s">
         <v>548</v>
@@ -7589,11 +7586,11 @@
       </c>
       <c r="L25" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M25" s="52" t="str">
         <f t="shared" si="9"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N25" s="52" t="str">
         <f t="shared" si="10"/>
@@ -7615,11 +7612,11 @@
       </c>
       <c r="S25" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T25" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U25" s="52" t="str">
         <f t="shared" si="15"/>
@@ -7646,18 +7643,18 @@
         <v>Management Discipline</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="50">
         <v>26</v>
       </c>
       <c r="B26" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E26" s="30" t="s">
         <v>548</v>
@@ -7682,11 +7679,11 @@
       </c>
       <c r="L26" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M26" s="52" t="str">
         <f t="shared" si="9"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N26" s="52" t="str">
         <f t="shared" si="10"/>
@@ -7708,11 +7705,11 @@
       </c>
       <c r="S26" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T26" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U26" s="52" t="str">
         <f t="shared" si="15"/>
@@ -7739,18 +7736,18 @@
         <v>Real Estate Discipline</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="50">
         <v>27</v>
       </c>
       <c r="B27" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E27" s="30" t="s">
         <v>548</v>
@@ -7775,11 +7772,11 @@
       </c>
       <c r="L27" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M27" s="52" t="str">
         <f t="shared" si="9"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N27" s="52" t="str">
         <f t="shared" si="10"/>
@@ -7801,11 +7798,11 @@
       </c>
       <c r="S27" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T27" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U27" s="52" t="str">
         <f t="shared" si="15"/>
@@ -7832,18 +7829,18 @@
         <v>Legislation Discipline</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="50">
         <v>28</v>
       </c>
       <c r="B28" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E28" s="30" t="s">
         <v>548</v>
@@ -7868,11 +7865,11 @@
       </c>
       <c r="L28" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M28" s="52" t="str">
         <f t="shared" si="9"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N28" s="52" t="str">
         <f t="shared" si="10"/>
@@ -7894,11 +7891,11 @@
       </c>
       <c r="S28" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T28" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U28" s="52" t="str">
         <f t="shared" si="15"/>
@@ -7925,18 +7922,18 @@
         <v>Discipline of Surveys and implementation</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="50">
         <v>29</v>
       </c>
       <c r="B29" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E29" s="30" t="s">
         <v>548</v>
@@ -7961,11 +7958,11 @@
       </c>
       <c r="L29" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M29" s="52" t="str">
         <f t="shared" si="9"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N29" s="52" t="str">
         <f t="shared" si="10"/>
@@ -7987,11 +7984,11 @@
       </c>
       <c r="S29" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T29" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U29" s="52" t="str">
         <f t="shared" si="15"/>
@@ -8018,18 +8015,18 @@
         <v>Operation Discipline</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="50">
         <v>30</v>
       </c>
       <c r="B30" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E30" s="30" t="s">
         <v>548</v>
@@ -8054,11 +8051,11 @@
       </c>
       <c r="L30" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M30" s="52" t="str">
         <f t="shared" si="9"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N30" s="52" t="str">
         <f t="shared" si="10"/>
@@ -8080,11 +8077,11 @@
       </c>
       <c r="S30" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T30" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U30" s="52" t="str">
         <f t="shared" si="15"/>
@@ -8111,18 +8108,18 @@
         <v>Other Disciplines</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="50">
         <v>31</v>
       </c>
       <c r="B31" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E31" s="30" t="s">
         <v>548</v>
@@ -8147,11 +8144,11 @@
       </c>
       <c r="L31" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M31" s="52" t="str">
         <f t="shared" si="9"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N31" s="52" t="str">
         <f t="shared" si="10"/>
@@ -8173,11 +8170,11 @@
       </c>
       <c r="S31" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T31" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U31" s="52" t="str">
         <f t="shared" si="15"/>
@@ -8204,18 +8201,18 @@
         <v>Planning Discipline</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" ht="7.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="50">
         <v>32</v>
       </c>
       <c r="B32" s="54" t="s">
-        <v>552</v>
+        <v>625</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="E32" s="30" t="s">
         <v>548</v>
@@ -8240,11 +8237,11 @@
       </c>
       <c r="L32" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M32" s="52" t="str">
         <f t="shared" si="9"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N32" s="52" t="str">
         <f t="shared" si="10"/>
@@ -8266,11 +8263,11 @@
       </c>
       <c r="S32" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T32" s="53" t="str">
         <f t="shared" si="15"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U32" s="52" t="str">
         <f t="shared" si="15"/>
@@ -8643,7 +8640,7 @@
         <v>380</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="D2" s="57" t="s">
         <v>196</v>
